--- a/diseases/d199/2010-2014.xlsx
+++ b/diseases/d199/2010-2014.xlsx
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1944,7 +1944,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3824,7 +3824,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
@@ -4764,7 +4764,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5704,7 +5704,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
@@ -6644,7 +6644,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7584,7 +7584,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK38" t="inlineStr">
@@ -8524,7 +8524,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9464,7 +9464,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
@@ -10404,7 +10404,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -11344,7 +11344,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK58" t="inlineStr">
@@ -12284,7 +12284,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13224,7 +13224,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK68" t="inlineStr">
@@ -14164,7 +14164,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -15104,7 +15104,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
@@ -16044,7 +16044,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -16984,7 +16984,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK88" t="inlineStr">
@@ -17924,7 +17924,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -18864,7 +18864,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK98" t="inlineStr">
@@ -19804,7 +19804,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -20744,7 +20744,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK108" t="inlineStr">
@@ -21684,7 +21684,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -22624,7 +22624,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK118" t="inlineStr">
@@ -23564,7 +23564,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -24504,7 +24504,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK128" t="inlineStr">
@@ -25444,7 +25444,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
@@ -26384,7 +26384,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK138" t="inlineStr">
@@ -27324,7 +27324,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK143" t="inlineStr">
@@ -28264,7 +28264,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK148" t="inlineStr">
@@ -29204,7 +29204,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -30144,7 +30144,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK158" t="inlineStr">
@@ -31084,7 +31084,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK163" t="inlineStr">
@@ -32024,7 +32024,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK168" t="inlineStr">
@@ -32964,7 +32964,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK173" t="inlineStr">
@@ -33904,7 +33904,7 @@
       </c>
       <c r="AJ178" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK178" t="inlineStr">
@@ -34844,7 +34844,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK183" t="inlineStr">
@@ -35784,7 +35784,7 @@
       </c>
       <c r="AJ188" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK188" t="inlineStr">
@@ -36724,7 +36724,7 @@
       </c>
       <c r="AJ193" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK193" t="inlineStr">
@@ -37664,7 +37664,7 @@
       </c>
       <c r="AJ198" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK198" t="inlineStr">
@@ -38604,7 +38604,7 @@
       </c>
       <c r="AJ203" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK203" t="inlineStr">
@@ -39544,7 +39544,7 @@
       </c>
       <c r="AJ208" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK208" t="inlineStr">
@@ -40484,7 +40484,7 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK213" t="inlineStr">
@@ -41424,7 +41424,7 @@
       </c>
       <c r="AJ218" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK218" t="inlineStr">
@@ -42364,7 +42364,7 @@
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK223" t="inlineStr">
@@ -43304,7 +43304,7 @@
       </c>
       <c r="AJ228" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK228" t="inlineStr">
@@ -44250,7 +44250,7 @@
       </c>
       <c r="AJ233" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK233" t="inlineStr">
@@ -44652,7 +44652,7 @@
       </c>
       <c r="AJ235" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK235" t="inlineStr">
@@ -45048,7 +45048,7 @@
       </c>
       <c r="AJ237" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK237" t="inlineStr">
@@ -45994,7 +45994,7 @@
       </c>
       <c r="AJ242" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK242" t="inlineStr">
@@ -46396,7 +46396,7 @@
       </c>
       <c r="AJ244" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK244" t="inlineStr">
@@ -46798,7 +46798,7 @@
       </c>
       <c r="AJ246" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK246" t="inlineStr">
@@ -47200,7 +47200,7 @@
       </c>
       <c r="AJ248" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK248" t="inlineStr">
@@ -47596,7 +47596,7 @@
       </c>
       <c r="AJ250" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK250" t="inlineStr">
@@ -48542,7 +48542,7 @@
       </c>
       <c r="AJ255" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK255" t="inlineStr">
@@ -48944,7 +48944,7 @@
       </c>
       <c r="AJ257" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK257" t="inlineStr">
@@ -49346,7 +49346,7 @@
       </c>
       <c r="AJ259" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK259" t="inlineStr">
@@ -49748,7 +49748,7 @@
       </c>
       <c r="AJ261" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK261" t="inlineStr">
@@ -50150,7 +50150,7 @@
       </c>
       <c r="AJ263" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK263" t="inlineStr">
@@ -50546,7 +50546,7 @@
       </c>
       <c r="AJ265" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK265" t="inlineStr">
@@ -51492,7 +51492,7 @@
       </c>
       <c r="AJ270" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK270" t="inlineStr">
@@ -51894,7 +51894,7 @@
       </c>
       <c r="AJ272" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK272" t="inlineStr">
@@ -52296,7 +52296,7 @@
       </c>
       <c r="AJ274" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK274" t="inlineStr">
@@ -52698,7 +52698,7 @@
       </c>
       <c r="AJ276" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK276" t="inlineStr">
@@ -53094,7 +53094,7 @@
       </c>
       <c r="AJ278" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK278" t="inlineStr">
@@ -54040,7 +54040,7 @@
       </c>
       <c r="AJ283" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK283" t="inlineStr">
@@ -54442,7 +54442,7 @@
       </c>
       <c r="AJ285" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK285" t="inlineStr">
@@ -54844,7 +54844,7 @@
       </c>
       <c r="AJ287" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK287" t="inlineStr">
@@ -55246,7 +55246,7 @@
       </c>
       <c r="AJ289" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK289" t="inlineStr">
@@ -55642,7 +55642,7 @@
       </c>
       <c r="AJ291" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK291" t="inlineStr">
@@ -56588,7 +56588,7 @@
       </c>
       <c r="AJ296" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK296" t="inlineStr">
@@ -56990,7 +56990,7 @@
       </c>
       <c r="AJ298" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK298" t="inlineStr">
@@ -57392,7 +57392,7 @@
       </c>
       <c r="AJ300" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK300" t="inlineStr">
@@ -57794,7 +57794,7 @@
       </c>
       <c r="AJ302" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK302" t="inlineStr">
@@ -58196,7 +58196,7 @@
       </c>
       <c r="AJ304" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK304" t="inlineStr">
@@ -58592,7 +58592,7 @@
       </c>
       <c r="AJ306" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK306" t="inlineStr">
@@ -59538,7 +59538,7 @@
       </c>
       <c r="AJ311" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK311" t="inlineStr">
@@ -59940,7 +59940,7 @@
       </c>
       <c r="AJ313" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK313" t="inlineStr">
@@ -60342,7 +60342,7 @@
       </c>
       <c r="AJ315" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK315" t="inlineStr">
@@ -60744,7 +60744,7 @@
       </c>
       <c r="AJ317" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK317" t="inlineStr">
@@ -61140,7 +61140,7 @@
       </c>
       <c r="AJ319" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK319" t="inlineStr">
@@ -62086,7 +62086,7 @@
       </c>
       <c r="AJ324" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK324" t="inlineStr">
@@ -62488,7 +62488,7 @@
       </c>
       <c r="AJ326" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK326" t="inlineStr">
@@ -62890,7 +62890,7 @@
       </c>
       <c r="AJ328" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK328" t="inlineStr">
@@ -63292,7 +63292,7 @@
       </c>
       <c r="AJ330" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK330" t="inlineStr">
@@ -63688,7 +63688,7 @@
       </c>
       <c r="AJ332" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK332" t="inlineStr">
@@ -64634,7 +64634,7 @@
       </c>
       <c r="AJ337" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK337" t="inlineStr">
@@ -65036,7 +65036,7 @@
       </c>
       <c r="AJ339" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK339" t="inlineStr">
@@ -65438,7 +65438,7 @@
       </c>
       <c r="AJ341" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK341" t="inlineStr">
@@ -65840,7 +65840,7 @@
       </c>
       <c r="AJ343" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK343" t="inlineStr">
@@ -66242,7 +66242,7 @@
       </c>
       <c r="AJ345" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK345" t="inlineStr">
@@ -66638,7 +66638,7 @@
       </c>
       <c r="AJ347" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK347" t="inlineStr">
@@ -67584,7 +67584,7 @@
       </c>
       <c r="AJ352" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK352" t="inlineStr">
@@ -67986,7 +67986,7 @@
       </c>
       <c r="AJ354" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK354" t="inlineStr">
@@ -68388,7 +68388,7 @@
       </c>
       <c r="AJ356" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK356" t="inlineStr">
@@ -68790,7 +68790,7 @@
       </c>
       <c r="AJ358" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK358" t="inlineStr">
@@ -69186,7 +69186,7 @@
       </c>
       <c r="AJ360" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK360" t="inlineStr">
@@ -70132,7 +70132,7 @@
       </c>
       <c r="AJ365" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK365" t="inlineStr">
@@ -70534,7 +70534,7 @@
       </c>
       <c r="AJ367" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK367" t="inlineStr">
@@ -70936,7 +70936,7 @@
       </c>
       <c r="AJ369" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK369" t="inlineStr">
@@ -71338,7 +71338,7 @@
       </c>
       <c r="AJ371" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK371" t="inlineStr">
@@ -71740,7 +71740,7 @@
       </c>
       <c r="AJ373" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK373" t="inlineStr">
@@ -72136,7 +72136,7 @@
       </c>
       <c r="AJ375" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK375" t="inlineStr">
@@ -73082,7 +73082,7 @@
       </c>
       <c r="AJ380" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK380" t="inlineStr">
@@ -73484,7 +73484,7 @@
       </c>
       <c r="AJ382" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK382" t="inlineStr">
@@ -73886,7 +73886,7 @@
       </c>
       <c r="AJ384" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK384" t="inlineStr">
@@ -74288,7 +74288,7 @@
       </c>
       <c r="AJ386" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK386" t="inlineStr">
@@ -74684,7 +74684,7 @@
       </c>
       <c r="AJ388" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK388" t="inlineStr">
@@ -75630,7 +75630,7 @@
       </c>
       <c r="AJ393" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK393" t="inlineStr">
@@ -76032,7 +76032,7 @@
       </c>
       <c r="AJ395" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK395" t="inlineStr">
@@ -76434,7 +76434,7 @@
       </c>
       <c r="AJ397" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK397" t="inlineStr">
@@ -76836,7 +76836,7 @@
       </c>
       <c r="AJ399" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK399" t="inlineStr">
@@ -77232,7 +77232,7 @@
       </c>
       <c r="AJ401" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK401" t="inlineStr">
@@ -78178,7 +78178,7 @@
       </c>
       <c r="AJ406" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK406" t="inlineStr">
@@ -78580,7 +78580,7 @@
       </c>
       <c r="AJ408" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK408" t="inlineStr">
@@ -78982,7 +78982,7 @@
       </c>
       <c r="AJ410" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK410" t="inlineStr">
@@ -79384,7 +79384,7 @@
       </c>
       <c r="AJ412" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK412" t="inlineStr">
@@ -79786,7 +79786,7 @@
       </c>
       <c r="AJ414" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK414" t="inlineStr">
@@ -80182,7 +80182,7 @@
       </c>
       <c r="AJ416" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK416" t="inlineStr">
@@ -81128,7 +81128,7 @@
       </c>
       <c r="AJ421" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK421" t="inlineStr">
@@ -81530,7 +81530,7 @@
       </c>
       <c r="AJ423" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK423" t="inlineStr">
@@ -81932,7 +81932,7 @@
       </c>
       <c r="AJ425" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK425" t="inlineStr">
@@ -82334,7 +82334,7 @@
       </c>
       <c r="AJ427" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK427" t="inlineStr">

--- a/diseases/d199/2010-2014.xlsx
+++ b/diseases/d199/2010-2014.xlsx
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1944,7 +1944,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3824,7 +3824,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
@@ -4764,7 +4764,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5704,7 +5704,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
@@ -6644,7 +6644,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7584,7 +7584,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK38" t="inlineStr">
@@ -8524,7 +8524,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9464,7 +9464,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
@@ -10404,7 +10404,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -11344,7 +11344,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK58" t="inlineStr">
@@ -12284,7 +12284,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13224,7 +13224,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK68" t="inlineStr">
@@ -14164,7 +14164,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -15104,7 +15104,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
@@ -16044,7 +16044,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -16984,7 +16984,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK88" t="inlineStr">
@@ -17924,7 +17924,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -18864,7 +18864,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK98" t="inlineStr">
@@ -19804,7 +19804,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -20744,7 +20744,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK108" t="inlineStr">
@@ -21684,7 +21684,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -22624,7 +22624,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK118" t="inlineStr">
@@ -23564,7 +23564,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -24504,7 +24504,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK128" t="inlineStr">
@@ -25444,7 +25444,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
@@ -26384,7 +26384,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK138" t="inlineStr">
@@ -27324,7 +27324,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK143" t="inlineStr">
@@ -28264,7 +28264,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK148" t="inlineStr">
@@ -29204,7 +29204,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -30144,7 +30144,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK158" t="inlineStr">
@@ -31084,7 +31084,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK163" t="inlineStr">
@@ -32024,7 +32024,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK168" t="inlineStr">
@@ -32964,7 +32964,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK173" t="inlineStr">
@@ -33904,7 +33904,7 @@
       </c>
       <c r="AJ178" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK178" t="inlineStr">
@@ -34844,7 +34844,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK183" t="inlineStr">
@@ -35784,7 +35784,7 @@
       </c>
       <c r="AJ188" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK188" t="inlineStr">
@@ -36724,7 +36724,7 @@
       </c>
       <c r="AJ193" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK193" t="inlineStr">
@@ -37664,7 +37664,7 @@
       </c>
       <c r="AJ198" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK198" t="inlineStr">
@@ -38604,7 +38604,7 @@
       </c>
       <c r="AJ203" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK203" t="inlineStr">
@@ -39544,7 +39544,7 @@
       </c>
       <c r="AJ208" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK208" t="inlineStr">
@@ -40484,7 +40484,7 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK213" t="inlineStr">
@@ -41424,7 +41424,7 @@
       </c>
       <c r="AJ218" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK218" t="inlineStr">
@@ -42364,7 +42364,7 @@
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK223" t="inlineStr">
@@ -43304,7 +43304,7 @@
       </c>
       <c r="AJ228" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK228" t="inlineStr">
@@ -44250,7 +44250,7 @@
       </c>
       <c r="AJ233" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK233" t="inlineStr">
@@ -44652,7 +44652,7 @@
       </c>
       <c r="AJ235" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK235" t="inlineStr">
@@ -45048,7 +45048,7 @@
       </c>
       <c r="AJ237" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK237" t="inlineStr">
@@ -45994,7 +45994,7 @@
       </c>
       <c r="AJ242" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK242" t="inlineStr">
@@ -46396,7 +46396,7 @@
       </c>
       <c r="AJ244" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK244" t="inlineStr">
@@ -46798,7 +46798,7 @@
       </c>
       <c r="AJ246" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK246" t="inlineStr">
@@ -47200,7 +47200,7 @@
       </c>
       <c r="AJ248" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK248" t="inlineStr">
@@ -47596,7 +47596,7 @@
       </c>
       <c r="AJ250" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK250" t="inlineStr">
@@ -48542,7 +48542,7 @@
       </c>
       <c r="AJ255" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK255" t="inlineStr">
@@ -48944,7 +48944,7 @@
       </c>
       <c r="AJ257" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK257" t="inlineStr">
@@ -49346,7 +49346,7 @@
       </c>
       <c r="AJ259" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK259" t="inlineStr">
@@ -49748,7 +49748,7 @@
       </c>
       <c r="AJ261" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK261" t="inlineStr">
@@ -50150,7 +50150,7 @@
       </c>
       <c r="AJ263" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK263" t="inlineStr">
@@ -50546,7 +50546,7 @@
       </c>
       <c r="AJ265" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK265" t="inlineStr">
@@ -51492,7 +51492,7 @@
       </c>
       <c r="AJ270" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK270" t="inlineStr">
@@ -51894,7 +51894,7 @@
       </c>
       <c r="AJ272" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK272" t="inlineStr">
@@ -52296,7 +52296,7 @@
       </c>
       <c r="AJ274" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK274" t="inlineStr">
@@ -52698,7 +52698,7 @@
       </c>
       <c r="AJ276" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK276" t="inlineStr">
@@ -53094,7 +53094,7 @@
       </c>
       <c r="AJ278" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK278" t="inlineStr">
@@ -54040,7 +54040,7 @@
       </c>
       <c r="AJ283" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK283" t="inlineStr">
@@ -54442,7 +54442,7 @@
       </c>
       <c r="AJ285" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK285" t="inlineStr">
@@ -54844,7 +54844,7 @@
       </c>
       <c r="AJ287" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK287" t="inlineStr">
@@ -55246,7 +55246,7 @@
       </c>
       <c r="AJ289" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK289" t="inlineStr">
@@ -55642,7 +55642,7 @@
       </c>
       <c r="AJ291" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK291" t="inlineStr">
@@ -56588,7 +56588,7 @@
       </c>
       <c r="AJ296" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK296" t="inlineStr">
@@ -56990,7 +56990,7 @@
       </c>
       <c r="AJ298" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK298" t="inlineStr">
@@ -57392,7 +57392,7 @@
       </c>
       <c r="AJ300" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK300" t="inlineStr">
@@ -57794,7 +57794,7 @@
       </c>
       <c r="AJ302" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK302" t="inlineStr">
@@ -58196,7 +58196,7 @@
       </c>
       <c r="AJ304" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK304" t="inlineStr">
@@ -58592,7 +58592,7 @@
       </c>
       <c r="AJ306" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK306" t="inlineStr">
@@ -59538,7 +59538,7 @@
       </c>
       <c r="AJ311" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK311" t="inlineStr">
@@ -59940,7 +59940,7 @@
       </c>
       <c r="AJ313" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK313" t="inlineStr">
@@ -60342,7 +60342,7 @@
       </c>
       <c r="AJ315" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK315" t="inlineStr">
@@ -60744,7 +60744,7 @@
       </c>
       <c r="AJ317" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK317" t="inlineStr">
@@ -61140,7 +61140,7 @@
       </c>
       <c r="AJ319" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK319" t="inlineStr">
@@ -62086,7 +62086,7 @@
       </c>
       <c r="AJ324" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK324" t="inlineStr">
@@ -62488,7 +62488,7 @@
       </c>
       <c r="AJ326" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK326" t="inlineStr">
@@ -62890,7 +62890,7 @@
       </c>
       <c r="AJ328" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK328" t="inlineStr">
@@ -63292,7 +63292,7 @@
       </c>
       <c r="AJ330" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK330" t="inlineStr">
@@ -63688,7 +63688,7 @@
       </c>
       <c r="AJ332" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK332" t="inlineStr">
@@ -64634,7 +64634,7 @@
       </c>
       <c r="AJ337" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK337" t="inlineStr">
@@ -65036,7 +65036,7 @@
       </c>
       <c r="AJ339" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK339" t="inlineStr">
@@ -65438,7 +65438,7 @@
       </c>
       <c r="AJ341" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK341" t="inlineStr">
@@ -65840,7 +65840,7 @@
       </c>
       <c r="AJ343" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK343" t="inlineStr">
@@ -66242,7 +66242,7 @@
       </c>
       <c r="AJ345" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK345" t="inlineStr">
@@ -66638,7 +66638,7 @@
       </c>
       <c r="AJ347" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK347" t="inlineStr">
@@ -67584,7 +67584,7 @@
       </c>
       <c r="AJ352" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK352" t="inlineStr">
@@ -67986,7 +67986,7 @@
       </c>
       <c r="AJ354" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK354" t="inlineStr">
@@ -68388,7 +68388,7 @@
       </c>
       <c r="AJ356" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK356" t="inlineStr">
@@ -68790,7 +68790,7 @@
       </c>
       <c r="AJ358" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK358" t="inlineStr">
@@ -69186,7 +69186,7 @@
       </c>
       <c r="AJ360" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK360" t="inlineStr">
@@ -70132,7 +70132,7 @@
       </c>
       <c r="AJ365" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK365" t="inlineStr">
@@ -70534,7 +70534,7 @@
       </c>
       <c r="AJ367" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK367" t="inlineStr">
@@ -70936,7 +70936,7 @@
       </c>
       <c r="AJ369" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK369" t="inlineStr">
@@ -71338,7 +71338,7 @@
       </c>
       <c r="AJ371" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK371" t="inlineStr">
@@ -71740,7 +71740,7 @@
       </c>
       <c r="AJ373" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK373" t="inlineStr">
@@ -72136,7 +72136,7 @@
       </c>
       <c r="AJ375" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK375" t="inlineStr">
@@ -73082,7 +73082,7 @@
       </c>
       <c r="AJ380" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK380" t="inlineStr">
@@ -73484,7 +73484,7 @@
       </c>
       <c r="AJ382" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK382" t="inlineStr">
@@ -73886,7 +73886,7 @@
       </c>
       <c r="AJ384" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK384" t="inlineStr">
@@ -74288,7 +74288,7 @@
       </c>
       <c r="AJ386" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK386" t="inlineStr">
@@ -74684,7 +74684,7 @@
       </c>
       <c r="AJ388" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK388" t="inlineStr">
@@ -75630,7 +75630,7 @@
       </c>
       <c r="AJ393" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK393" t="inlineStr">
@@ -76032,7 +76032,7 @@
       </c>
       <c r="AJ395" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK395" t="inlineStr">
@@ -76434,7 +76434,7 @@
       </c>
       <c r="AJ397" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK397" t="inlineStr">
@@ -76836,7 +76836,7 @@
       </c>
       <c r="AJ399" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK399" t="inlineStr">
@@ -77232,7 +77232,7 @@
       </c>
       <c r="AJ401" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK401" t="inlineStr">
@@ -78178,7 +78178,7 @@
       </c>
       <c r="AJ406" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK406" t="inlineStr">
@@ -78580,7 +78580,7 @@
       </c>
       <c r="AJ408" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK408" t="inlineStr">
@@ -78982,7 +78982,7 @@
       </c>
       <c r="AJ410" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK410" t="inlineStr">
@@ -79384,7 +79384,7 @@
       </c>
       <c r="AJ412" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK412" t="inlineStr">
@@ -79786,7 +79786,7 @@
       </c>
       <c r="AJ414" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK414" t="inlineStr">
@@ -80182,7 +80182,7 @@
       </c>
       <c r="AJ416" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK416" t="inlineStr">
@@ -81128,7 +81128,7 @@
       </c>
       <c r="AJ421" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK421" t="inlineStr">
@@ -81530,7 +81530,7 @@
       </c>
       <c r="AJ423" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK423" t="inlineStr">
@@ -81932,7 +81932,7 @@
       </c>
       <c r="AJ425" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK425" t="inlineStr">
@@ -82334,7 +82334,7 @@
       </c>
       <c r="AJ427" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK427" t="inlineStr">

--- a/diseases/d199/2010-2014.xlsx
+++ b/diseases/d199/2010-2014.xlsx
@@ -1309,9 +1309,6 @@
       <c r="O5" t="n">
         <v>69</v>
       </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
       <c r="R5" t="n">
         <v>1.286509244547788</v>
       </c>
@@ -2249,9 +2246,6 @@
       <c r="O10" t="n">
         <v>63</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="R10" t="n">
         <v>1.174638875456676</v>
       </c>
@@ -3189,9 +3183,6 @@
       <c r="O15" t="n">
         <v>81</v>
       </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
       <c r="R15" t="n">
         <v>1.510249982730012</v>
       </c>
@@ -4129,9 +4120,6 @@
       <c r="O20" t="n">
         <v>59</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="R20" t="n">
         <v>1.100058629395934</v>
       </c>
@@ -5069,9 +5057,6 @@
       <c r="O25" t="n">
         <v>53</v>
       </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
       <c r="R25" t="n">
         <v>0.9881882603048225</v>
       </c>
@@ -6009,9 +5994,6 @@
       <c r="O30" t="n">
         <v>33</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="R30" t="n">
         <v>0.615287030001116</v>
       </c>
@@ -6949,9 +6931,6 @@
       <c r="O35" t="n">
         <v>17</v>
       </c>
-      <c r="Q35" t="n">
-        <v>0</v>
-      </c>
       <c r="R35" t="n">
         <v>0.3169660457581506</v>
       </c>
@@ -7889,9 +7868,6 @@
       <c r="O40" t="n">
         <v>13</v>
       </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
       <c r="R40" t="n">
         <v>0.2423857996974093</v>
       </c>
@@ -8829,9 +8805,6 @@
       <c r="O45" t="n">
         <v>5</v>
       </c>
-      <c r="Q45" t="n">
-        <v>0</v>
-      </c>
       <c r="R45" t="n">
         <v>0.09322530757592666</v>
       </c>
@@ -9769,9 +9742,6 @@
       <c r="O50" t="n">
         <v>9</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="R50" t="n">
         <v>0.167805553636668</v>
       </c>
@@ -10709,9 +10679,6 @@
       <c r="O55" t="n">
         <v>11</v>
       </c>
-      <c r="Q55" t="n">
-        <v>0</v>
-      </c>
       <c r="R55" t="n">
         <v>0.2050956766670386</v>
       </c>
@@ -11649,9 +11616,6 @@
       <c r="O60" t="n">
         <v>13</v>
       </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
       <c r="R60" t="n">
         <v>0.2423857996974093</v>
       </c>
@@ -12589,9 +12553,6 @@
       <c r="O65" t="n">
         <v>30</v>
       </c>
-      <c r="Q65" t="n">
-        <v>0</v>
-      </c>
       <c r="R65" t="n">
         <v>0.5567679693614298</v>
       </c>
@@ -13529,9 +13490,6 @@
       <c r="O70" t="n">
         <v>42</v>
       </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
       <c r="R70" t="n">
         <v>0.7794751571060018</v>
       </c>
@@ -14469,9 +14427,6 @@
       <c r="O75" t="n">
         <v>69</v>
       </c>
-      <c r="Q75" t="n">
-        <v>0</v>
-      </c>
       <c r="R75" t="n">
         <v>1.280566329531289</v>
       </c>
@@ -15409,9 +15364,6 @@
       <c r="O80" t="n">
         <v>39</v>
       </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
       <c r="R80" t="n">
         <v>0.7237983601698588</v>
       </c>
@@ -16349,9 +16301,6 @@
       <c r="O85" t="n">
         <v>46</v>
       </c>
-      <c r="Q85" t="n">
-        <v>0</v>
-      </c>
       <c r="R85" t="n">
         <v>0.8537108863541925</v>
       </c>
@@ -17289,9 +17238,6 @@
       <c r="O90" t="n">
         <v>16</v>
       </c>
-      <c r="Q90" t="n">
-        <v>0</v>
-      </c>
       <c r="R90" t="n">
         <v>0.2969429169927626</v>
       </c>
@@ -18229,9 +18175,6 @@
       <c r="O95" t="n">
         <v>11</v>
       </c>
-      <c r="Q95" t="n">
-        <v>0</v>
-      </c>
       <c r="R95" t="n">
         <v>0.2041482554325243</v>
       </c>
@@ -19169,9 +19112,6 @@
       <c r="O100" t="n">
         <v>7</v>
       </c>
-      <c r="Q100" t="n">
-        <v>0</v>
-      </c>
       <c r="R100" t="n">
         <v>0.1299125261843336</v>
       </c>
@@ -20109,9 +20049,6 @@
       <c r="O105" t="n">
         <v>4</v>
       </c>
-      <c r="Q105" t="n">
-        <v>0</v>
-      </c>
       <c r="R105" t="n">
         <v>0.07423572924819065</v>
       </c>
@@ -21049,9 +20986,6 @@
       <c r="O110" t="n">
         <v>12</v>
       </c>
-      <c r="Q110" t="n">
-        <v>0</v>
-      </c>
       <c r="R110" t="n">
         <v>0.2227071877445719</v>
       </c>
@@ -21989,9 +21923,6 @@
       <c r="O115" t="n">
         <v>9</v>
       </c>
-      <c r="Q115" t="n">
-        <v>0</v>
-      </c>
       <c r="R115" t="n">
         <v>0.1670303908084289</v>
       </c>
@@ -22929,9 +22860,6 @@
       <c r="O120" t="n">
         <v>7</v>
       </c>
-      <c r="Q120" t="n">
-        <v>0</v>
-      </c>
       <c r="R120" t="n">
         <v>0.1299125261843336</v>
       </c>
@@ -23869,9 +23797,6 @@
       <c r="O125" t="n">
         <v>16</v>
       </c>
-      <c r="Q125" t="n">
-        <v>0</v>
-      </c>
       <c r="R125" t="n">
         <v>0.295531662846766</v>
       </c>
@@ -24809,9 +24734,6 @@
       <c r="O130" t="n">
         <v>18</v>
       </c>
-      <c r="Q130" t="n">
-        <v>0</v>
-      </c>
       <c r="R130" t="n">
         <v>0.3324731207026118</v>
       </c>
@@ -25749,9 +25671,6 @@
       <c r="O135" t="n">
         <v>22</v>
       </c>
-      <c r="Q135" t="n">
-        <v>0</v>
-      </c>
       <c r="R135" t="n">
         <v>0.4063560364143033</v>
       </c>
@@ -26689,9 +26608,6 @@
       <c r="O140" t="n">
         <v>27</v>
       </c>
-      <c r="Q140" t="n">
-        <v>0</v>
-      </c>
       <c r="R140" t="n">
         <v>0.4987096810539177</v>
       </c>
@@ -27629,9 +27545,6 @@
       <c r="O145" t="n">
         <v>32</v>
       </c>
-      <c r="Q145" t="n">
-        <v>0</v>
-      </c>
       <c r="R145" t="n">
         <v>0.591063325693532</v>
       </c>
@@ -28569,9 +28482,6 @@
       <c r="O150" t="n">
         <v>23</v>
       </c>
-      <c r="Q150" t="n">
-        <v>0</v>
-      </c>
       <c r="R150" t="n">
         <v>0.4248267653422261</v>
       </c>
@@ -29509,9 +29419,6 @@
       <c r="O155" t="n">
         <v>13</v>
       </c>
-      <c r="Q155" t="n">
-        <v>0</v>
-      </c>
       <c r="R155" t="n">
         <v>0.2401194760629974</v>
       </c>
@@ -30449,9 +30356,6 @@
       <c r="O160" t="n">
         <v>12</v>
       </c>
-      <c r="Q160" t="n">
-        <v>0</v>
-      </c>
       <c r="R160" t="n">
         <v>0.2216487471350745</v>
       </c>
@@ -31389,9 +31293,6 @@
       <c r="O165" t="n">
         <v>9</v>
       </c>
-      <c r="Q165" t="n">
-        <v>0</v>
-      </c>
       <c r="R165" t="n">
         <v>0.1662365603513059</v>
       </c>
@@ -32329,9 +32230,6 @@
       <c r="O170" t="n">
         <v>13</v>
       </c>
-      <c r="Q170" t="n">
-        <v>0</v>
-      </c>
       <c r="R170" t="n">
         <v>0.2401194760629974</v>
       </c>
@@ -33269,9 +33167,6 @@
       <c r="O175" t="n">
         <v>5</v>
       </c>
-      <c r="Q175" t="n">
-        <v>0</v>
-      </c>
       <c r="R175" t="n">
         <v>0.09235364463961437</v>
       </c>
@@ -34209,9 +34104,6 @@
       <c r="O180" t="n">
         <v>19</v>
       </c>
-      <c r="Q180" t="n">
-        <v>0</v>
-      </c>
       <c r="R180" t="n">
         <v>0.3509438496305346</v>
       </c>
@@ -35149,9 +35041,6 @@
       <c r="O185" t="n">
         <v>29</v>
       </c>
-      <c r="Q185" t="n">
-        <v>0</v>
-      </c>
       <c r="R185" t="n">
         <v>0.5331810519220901</v>
       </c>
@@ -36089,9 +35978,6 @@
       <c r="O190" t="n">
         <v>35</v>
       </c>
-      <c r="Q190" t="n">
-        <v>0</v>
-      </c>
       <c r="R190" t="n">
         <v>0.6434943730094191</v>
       </c>
@@ -37029,9 +36915,6 @@
       <c r="O195" t="n">
         <v>34</v>
       </c>
-      <c r="Q195" t="n">
-        <v>0</v>
-      </c>
       <c r="R195" t="n">
         <v>0.6251088194948643</v>
       </c>
@@ -37969,9 +37852,6 @@
       <c r="O200" t="n">
         <v>45</v>
       </c>
-      <c r="Q200" t="n">
-        <v>0</v>
-      </c>
       <c r="R200" t="n">
         <v>0.8273499081549675</v>
       </c>
@@ -38909,9 +38789,6 @@
       <c r="O205" t="n">
         <v>46</v>
       </c>
-      <c r="Q205" t="n">
-        <v>0</v>
-      </c>
       <c r="R205" t="n">
         <v>0.8457354616695223</v>
       </c>
@@ -39849,9 +39726,6 @@
       <c r="O210" t="n">
         <v>24</v>
       </c>
-      <c r="Q210" t="n">
-        <v>0</v>
-      </c>
       <c r="R210" t="n">
         <v>0.441253284349316</v>
       </c>
@@ -40789,9 +40663,6 @@
       <c r="O215" t="n">
         <v>12</v>
       </c>
-      <c r="Q215" t="n">
-        <v>0</v>
-      </c>
       <c r="R215" t="n">
         <v>0.220626642174658</v>
       </c>
@@ -41729,9 +41600,6 @@
       <c r="O220" t="n">
         <v>6</v>
       </c>
-      <c r="Q220" t="n">
-        <v>0</v>
-      </c>
       <c r="R220" t="n">
         <v>0.110313321087329</v>
       </c>
@@ -42669,9 +42537,6 @@
       <c r="O225" t="n">
         <v>7</v>
       </c>
-      <c r="Q225" t="n">
-        <v>0</v>
-      </c>
       <c r="R225" t="n">
         <v>0.1286988746018838</v>
       </c>
@@ -43609,9 +43474,6 @@
       <c r="O230" t="n">
         <v>7</v>
       </c>
-      <c r="Q230" t="n">
-        <v>0</v>
-      </c>
       <c r="R230" t="n">
         <v>0.1286988746018838</v>
       </c>
@@ -44008,9 +43870,6 @@
       <c r="P232" t="n">
         <v>2</v>
       </c>
-      <c r="Q232" t="n">
-        <v>0</v>
-      </c>
       <c r="R232" t="n">
         <v>0.001565880767159907</v>
       </c>
@@ -44260,7 +44119,7 @@
       </c>
       <c r="AM233" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN233" t="b">
@@ -44410,9 +44269,6 @@
       <c r="P234" t="n">
         <v>1</v>
       </c>
-      <c r="Q234" t="n">
-        <v>0</v>
-      </c>
       <c r="R234" t="n">
         <v>0.0007829403835799535</v>
       </c>
@@ -44662,7 +44518,7 @@
       </c>
       <c r="AM235" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN235" t="b">
@@ -45353,9 +45209,6 @@
       <c r="O239" t="n">
         <v>20</v>
       </c>
-      <c r="Q239" t="n">
-        <v>0</v>
-      </c>
       <c r="R239" t="n">
         <v>0.3677110702910966</v>
       </c>
@@ -45752,9 +45605,6 @@
       <c r="P241" t="n">
         <v>6</v>
       </c>
-      <c r="Q241" t="n">
-        <v>0</v>
-      </c>
       <c r="R241" t="n">
         <v>0.004697642301479722</v>
       </c>
@@ -46004,7 +45854,7 @@
       </c>
       <c r="AM242" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN242" t="b">
@@ -46154,9 +46004,6 @@
       <c r="P243" t="n">
         <v>9</v>
       </c>
-      <c r="Q243" t="n">
-        <v>0</v>
-      </c>
       <c r="R243" t="n">
         <v>0.007046463452219581</v>
       </c>
@@ -46406,7 +46253,7 @@
       </c>
       <c r="AM244" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN244" t="b">
@@ -46556,9 +46403,6 @@
       <c r="P245" t="n">
         <v>4</v>
       </c>
-      <c r="Q245" t="n">
-        <v>0</v>
-      </c>
       <c r="R245" t="n">
         <v>0.003131761534319814</v>
       </c>
@@ -46808,7 +46652,7 @@
       </c>
       <c r="AM246" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN246" t="b">
@@ -46958,9 +46802,6 @@
       <c r="P247" t="n">
         <v>12</v>
       </c>
-      <c r="Q247" t="n">
-        <v>0</v>
-      </c>
       <c r="R247" t="n">
         <v>0.009395284602959443</v>
       </c>
@@ -47210,7 +47051,7 @@
       </c>
       <c r="AM248" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN248" t="b">
@@ -47901,9 +47742,6 @@
       <c r="O252" t="n">
         <v>17</v>
       </c>
-      <c r="Q252" t="n">
-        <v>0</v>
-      </c>
       <c r="R252" t="n">
         <v>0.3125544097474321</v>
       </c>
@@ -48300,9 +48138,6 @@
       <c r="P254" t="n">
         <v>23</v>
       </c>
-      <c r="Q254" t="n">
-        <v>0</v>
-      </c>
       <c r="R254" t="n">
         <v>0.01800762882233893</v>
       </c>
@@ -48552,7 +48387,7 @@
       </c>
       <c r="AM255" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN255" t="b">
@@ -48702,9 +48537,6 @@
       <c r="P256" t="n">
         <v>18</v>
       </c>
-      <c r="Q256" t="n">
-        <v>0</v>
-      </c>
       <c r="R256" t="n">
         <v>0.01409292690443916</v>
       </c>
@@ -48954,7 +48786,7 @@
       </c>
       <c r="AM257" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN257" t="b">
@@ -49104,9 +48936,6 @@
       <c r="P258" t="n">
         <v>19</v>
       </c>
-      <c r="Q258" t="n">
-        <v>0</v>
-      </c>
       <c r="R258" t="n">
         <v>0.01487586728801911</v>
       </c>
@@ -49356,7 +49185,7 @@
       </c>
       <c r="AM259" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN259" t="b">
@@ -49506,9 +49335,6 @@
       <c r="P260" t="n">
         <v>39</v>
       </c>
-      <c r="Q260" t="n">
-        <v>0</v>
-      </c>
       <c r="R260" t="n">
         <v>0.03053467495961818</v>
       </c>
@@ -49758,7 +49584,7 @@
       </c>
       <c r="AM261" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN261" t="b">
@@ -49908,9 +49734,6 @@
       <c r="P262" t="n">
         <v>25</v>
       </c>
-      <c r="Q262" t="n">
-        <v>0</v>
-      </c>
       <c r="R262" t="n">
         <v>0.01957350958949884</v>
       </c>
@@ -50160,7 +49983,7 @@
       </c>
       <c r="AM263" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN263" t="b">
@@ -50851,9 +50674,6 @@
       <c r="O267" t="n">
         <v>28</v>
       </c>
-      <c r="Q267" t="n">
-        <v>0</v>
-      </c>
       <c r="R267" t="n">
         <v>0.5126623949682918</v>
       </c>
@@ -51250,9 +51070,6 @@
       <c r="P269" t="n">
         <v>33</v>
       </c>
-      <c r="Q269" t="n">
-        <v>0</v>
-      </c>
       <c r="R269" t="n">
         <v>0.02588507249795017</v>
       </c>
@@ -51502,7 +51319,7 @@
       </c>
       <c r="AM270" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN270" t="b">
@@ -51652,9 +51469,6 @@
       <c r="P271" t="n">
         <v>38</v>
       </c>
-      <c r="Q271" t="n">
-        <v>0</v>
-      </c>
       <c r="R271" t="n">
         <v>0.02980705317945777</v>
       </c>
@@ -51904,7 +51718,7 @@
       </c>
       <c r="AM272" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN272" t="b">
@@ -52054,9 +51868,6 @@
       <c r="P273" t="n">
         <v>41</v>
       </c>
-      <c r="Q273" t="n">
-        <v>0</v>
-      </c>
       <c r="R273" t="n">
         <v>0.03216024158836233</v>
       </c>
@@ -52306,7 +52117,7 @@
       </c>
       <c r="AM274" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN274" t="b">
@@ -52456,9 +52267,6 @@
       <c r="P275" t="n">
         <v>68</v>
       </c>
-      <c r="Q275" t="n">
-        <v>0</v>
-      </c>
       <c r="R275" t="n">
         <v>0.05333893726850337</v>
       </c>
@@ -52708,7 +52516,7 @@
       </c>
       <c r="AM276" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN276" t="b">
@@ -53399,9 +53207,6 @@
       <c r="O280" t="n">
         <v>28</v>
       </c>
-      <c r="Q280" t="n">
-        <v>0</v>
-      </c>
       <c r="R280" t="n">
         <v>0.5126623949682918</v>
       </c>
@@ -53798,9 +53603,6 @@
       <c r="P282" t="n">
         <v>56</v>
       </c>
-      <c r="Q282" t="n">
-        <v>0</v>
-      </c>
       <c r="R282" t="n">
         <v>0.04392618363288513</v>
       </c>
@@ -54050,7 +53852,7 @@
       </c>
       <c r="AM283" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN283" t="b">
@@ -54200,9 +54002,6 @@
       <c r="P284" t="n">
         <v>59</v>
       </c>
-      <c r="Q284" t="n">
-        <v>0</v>
-      </c>
       <c r="R284" t="n">
         <v>0.04627937204178969</v>
       </c>
@@ -54452,7 +54251,7 @@
       </c>
       <c r="AM285" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN285" t="b">
@@ -54602,9 +54401,6 @@
       <c r="P286" t="n">
         <v>70</v>
       </c>
-      <c r="Q286" t="n">
-        <v>0</v>
-      </c>
       <c r="R286" t="n">
         <v>0.05490772954110641</v>
       </c>
@@ -54854,7 +54650,7 @@
       </c>
       <c r="AM287" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN287" t="b">
@@ -55004,9 +54800,6 @@
       <c r="P288" t="n">
         <v>57</v>
       </c>
-      <c r="Q288" t="n">
-        <v>0</v>
-      </c>
       <c r="R288" t="n">
         <v>0.04471057976918665</v>
       </c>
@@ -55256,7 +55049,7 @@
       </c>
       <c r="AM289" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN289" t="b">
@@ -55947,9 +55740,6 @@
       <c r="O293" t="n">
         <v>34</v>
       </c>
-      <c r="Q293" t="n">
-        <v>0</v>
-      </c>
       <c r="R293" t="n">
         <v>0.6225186224614973</v>
       </c>
@@ -56346,9 +56136,6 @@
       <c r="P295" t="n">
         <v>85</v>
       </c>
-      <c r="Q295" t="n">
-        <v>0</v>
-      </c>
       <c r="R295" t="n">
         <v>0.06667367158562922</v>
       </c>
@@ -56598,7 +56385,7 @@
       </c>
       <c r="AM296" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN296" t="b">
@@ -56748,9 +56535,6 @@
       <c r="P297" t="n">
         <v>80</v>
       </c>
-      <c r="Q297" t="n">
-        <v>0</v>
-      </c>
       <c r="R297" t="n">
         <v>0.06275169090412161</v>
       </c>
@@ -57000,7 +56784,7 @@
       </c>
       <c r="AM298" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN298" t="b">
@@ -57150,9 +56934,6 @@
       <c r="P299" t="n">
         <v>87</v>
       </c>
-      <c r="Q299" t="n">
-        <v>0</v>
-      </c>
       <c r="R299" t="n">
         <v>0.06824246385823225</v>
       </c>
@@ -57402,7 +57183,7 @@
       </c>
       <c r="AM300" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN300" t="b">
@@ -57552,9 +57333,6 @@
       <c r="P301" t="n">
         <v>133</v>
       </c>
-      <c r="Q301" t="n">
-        <v>0</v>
-      </c>
       <c r="R301" t="n">
         <v>0.1043246861281022</v>
       </c>
@@ -57804,7 +57582,7 @@
       </c>
       <c r="AM302" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN302" t="b">
@@ -57954,9 +57732,6 @@
       <c r="P303" t="n">
         <v>132</v>
       </c>
-      <c r="Q303" t="n">
-        <v>0</v>
-      </c>
       <c r="R303" t="n">
         <v>0.1035402899918007</v>
       </c>
@@ -58206,7 +57981,7 @@
       </c>
       <c r="AM304" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN304" t="b">
@@ -58897,9 +58672,6 @@
       <c r="O308" t="n">
         <v>44</v>
       </c>
-      <c r="Q308" t="n">
-        <v>0</v>
-      </c>
       <c r="R308" t="n">
         <v>0.8056123349501728</v>
       </c>
@@ -59296,9 +59068,6 @@
       <c r="P310" t="n">
         <v>123</v>
       </c>
-      <c r="Q310" t="n">
-        <v>0</v>
-      </c>
       <c r="R310" t="n">
         <v>0.09648072476508698</v>
       </c>
@@ -59548,7 +59317,7 @@
       </c>
       <c r="AM311" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN311" t="b">
@@ -59698,9 +59467,6 @@
       <c r="P312" t="n">
         <v>183</v>
       </c>
-      <c r="Q312" t="n">
-        <v>0</v>
-      </c>
       <c r="R312" t="n">
         <v>0.1435444929431782</v>
       </c>
@@ -59950,7 +59716,7 @@
       </c>
       <c r="AM313" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN313" t="b">
@@ -60100,9 +59866,6 @@
       <c r="P314" t="n">
         <v>261</v>
       </c>
-      <c r="Q314" t="n">
-        <v>0</v>
-      </c>
       <c r="R314" t="n">
         <v>0.2047273915746968</v>
       </c>
@@ -60352,7 +60115,7 @@
       </c>
       <c r="AM315" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN315" t="b">
@@ -60502,9 +60265,6 @@
       <c r="P316" t="n">
         <v>328</v>
       </c>
-      <c r="Q316" t="n">
-        <v>0</v>
-      </c>
       <c r="R316" t="n">
         <v>0.2572819327068986</v>
       </c>
@@ -60754,7 +60514,7 @@
       </c>
       <c r="AM317" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN317" t="b">
@@ -61445,9 +61205,6 @@
       <c r="O321" t="n">
         <v>40</v>
       </c>
-      <c r="Q321" t="n">
-        <v>0</v>
-      </c>
       <c r="R321" t="n">
         <v>0.7323748499547026</v>
       </c>
@@ -61844,9 +61601,6 @@
       <c r="P323" t="n">
         <v>375</v>
       </c>
-      <c r="Q323" t="n">
-        <v>0</v>
-      </c>
       <c r="R323" t="n">
         <v>0.2941485511130701</v>
       </c>
@@ -62096,7 +61850,7 @@
       </c>
       <c r="AM324" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN324" t="b">
@@ -62246,9 +62000,6 @@
       <c r="P325" t="n">
         <v>275</v>
       </c>
-      <c r="Q325" t="n">
-        <v>0</v>
-      </c>
       <c r="R325" t="n">
         <v>0.2157089374829181</v>
       </c>
@@ -62498,7 +62249,7 @@
       </c>
       <c r="AM326" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN326" t="b">
@@ -62648,9 +62399,6 @@
       <c r="P327" t="n">
         <v>314</v>
       </c>
-      <c r="Q327" t="n">
-        <v>0</v>
-      </c>
       <c r="R327" t="n">
         <v>0.2463003867986774</v>
       </c>
@@ -62900,7 +62648,7 @@
       </c>
       <c r="AM328" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN328" t="b">
@@ -63050,9 +62798,6 @@
       <c r="P329" t="n">
         <v>300</v>
       </c>
-      <c r="Q329" t="n">
-        <v>0</v>
-      </c>
       <c r="R329" t="n">
         <v>0.235318840890456</v>
       </c>
@@ -63302,7 +63047,7 @@
       </c>
       <c r="AM330" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN330" t="b">
@@ -63993,9 +63738,6 @@
       <c r="O334" t="n">
         <v>16</v>
       </c>
-      <c r="Q334" t="n">
-        <v>0</v>
-      </c>
       <c r="R334" t="n">
         <v>0.292949939981881</v>
       </c>
@@ -64392,9 +64134,6 @@
       <c r="P336" t="n">
         <v>224</v>
       </c>
-      <c r="Q336" t="n">
-        <v>0</v>
-      </c>
       <c r="R336" t="n">
         <v>0.1757047345315405</v>
       </c>
@@ -64644,7 +64383,7 @@
       </c>
       <c r="AM337" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN337" t="b">
@@ -64794,9 +64533,6 @@
       <c r="P338" t="n">
         <v>148</v>
       </c>
-      <c r="Q338" t="n">
-        <v>0</v>
-      </c>
       <c r="R338" t="n">
         <v>0.116090628172625</v>
       </c>
@@ -65046,7 +64782,7 @@
       </c>
       <c r="AM339" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN339" t="b">
@@ -65196,9 +64932,6 @@
       <c r="P340" t="n">
         <v>95</v>
       </c>
-      <c r="Q340" t="n">
-        <v>0</v>
-      </c>
       <c r="R340" t="n">
         <v>0.07451763294864443</v>
       </c>
@@ -65448,7 +65181,7 @@
       </c>
       <c r="AM341" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN341" t="b">
@@ -65598,9 +65331,6 @@
       <c r="P342" t="n">
         <v>66</v>
       </c>
-      <c r="Q342" t="n">
-        <v>0</v>
-      </c>
       <c r="R342" t="n">
         <v>0.05177014499590033</v>
       </c>
@@ -65850,7 +65580,7 @@
       </c>
       <c r="AM343" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN343" t="b">
@@ -66000,9 +65730,6 @@
       <c r="P344" t="n">
         <v>54</v>
       </c>
-      <c r="Q344" t="n">
-        <v>0</v>
-      </c>
       <c r="R344" t="n">
         <v>0.04235739136028209</v>
       </c>
@@ -66252,7 +65979,7 @@
       </c>
       <c r="AM345" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN345" t="b">
@@ -66943,9 +66670,6 @@
       <c r="O349" t="n">
         <v>25</v>
       </c>
-      <c r="Q349" t="n">
-        <v>0</v>
-      </c>
       <c r="R349" t="n">
         <v>0.4577342812216891</v>
       </c>
@@ -67342,9 +67066,6 @@
       <c r="P351" t="n">
         <v>35</v>
       </c>
-      <c r="Q351" t="n">
-        <v>0</v>
-      </c>
       <c r="R351" t="n">
         <v>0.02745386477055321</v>
       </c>
@@ -67594,7 +67315,7 @@
       </c>
       <c r="AM352" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN352" t="b">
@@ -67744,9 +67465,6 @@
       <c r="P353" t="n">
         <v>30</v>
       </c>
-      <c r="Q353" t="n">
-        <v>0</v>
-      </c>
       <c r="R353" t="n">
         <v>0.02353188408904561</v>
       </c>
@@ -67996,7 +67714,7 @@
       </c>
       <c r="AM354" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN354" t="b">
@@ -68146,9 +67864,6 @@
       <c r="P355" t="n">
         <v>10</v>
       </c>
-      <c r="Q355" t="n">
-        <v>0</v>
-      </c>
       <c r="R355" t="n">
         <v>0.007843961363015201</v>
       </c>
@@ -68398,7 +68113,7 @@
       </c>
       <c r="AM356" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN356" t="b">
@@ -68548,9 +68263,6 @@
       <c r="P357" t="n">
         <v>7</v>
       </c>
-      <c r="Q357" t="n">
-        <v>0</v>
-      </c>
       <c r="R357" t="n">
         <v>0.005490772954110641</v>
       </c>
@@ -68800,7 +68512,7 @@
       </c>
       <c r="AM358" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN358" t="b">
@@ -69491,9 +69203,6 @@
       <c r="O362" t="n">
         <v>14</v>
       </c>
-      <c r="Q362" t="n">
-        <v>0</v>
-      </c>
       <c r="R362" t="n">
         <v>0.2563311974841459</v>
       </c>
@@ -69890,9 +69599,6 @@
       <c r="P364" t="n">
         <v>5</v>
       </c>
-      <c r="Q364" t="n">
-        <v>0</v>
-      </c>
       <c r="R364" t="n">
         <v>0.003921980681507601</v>
       </c>
@@ -70142,7 +69848,7 @@
       </c>
       <c r="AM365" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN365" t="b">
@@ -70292,9 +69998,6 @@
       <c r="P366" t="n">
         <v>4</v>
       </c>
-      <c r="Q366" t="n">
-        <v>0</v>
-      </c>
       <c r="R366" t="n">
         <v>0.003137584545206081</v>
       </c>
@@ -70544,7 +70247,7 @@
       </c>
       <c r="AM367" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN367" t="b">
@@ -70694,9 +70397,6 @@
       <c r="P368" t="n">
         <v>1</v>
       </c>
-      <c r="Q368" t="n">
-        <v>0</v>
-      </c>
       <c r="R368" t="n">
         <v>0.0007843961363015203</v>
       </c>
@@ -70946,7 +70646,7 @@
       </c>
       <c r="AM369" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN369" t="b">
@@ -71096,9 +70796,6 @@
       <c r="P370" t="n">
         <v>1</v>
       </c>
-      <c r="Q370" t="n">
-        <v>0</v>
-      </c>
       <c r="R370" t="n">
         <v>0.0007843961363015203</v>
       </c>
@@ -71348,7 +71045,7 @@
       </c>
       <c r="AM371" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN371" t="b">
@@ -71498,9 +71195,6 @@
       <c r="P372" t="n">
         <v>5</v>
       </c>
-      <c r="Q372" t="n">
-        <v>0</v>
-      </c>
       <c r="R372" t="n">
         <v>0.003921980681507601</v>
       </c>
@@ -71750,7 +71444,7 @@
       </c>
       <c r="AM373" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN373" t="b">
@@ -72441,9 +72135,6 @@
       <c r="O377" t="n">
         <v>8</v>
       </c>
-      <c r="Q377" t="n">
-        <v>0</v>
-      </c>
       <c r="R377" t="n">
         <v>0.1464749699909405</v>
       </c>
@@ -72840,9 +72531,6 @@
       <c r="P379" t="n">
         <v>5</v>
       </c>
-      <c r="Q379" t="n">
-        <v>0</v>
-      </c>
       <c r="R379" t="n">
         <v>0.003921980681507601</v>
       </c>
@@ -73092,7 +72780,7 @@
       </c>
       <c r="AM380" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN380" t="b">
@@ -73242,9 +72930,6 @@
       <c r="P381" t="n">
         <v>4</v>
       </c>
-      <c r="Q381" t="n">
-        <v>0</v>
-      </c>
       <c r="R381" t="n">
         <v>0.003137584545206081</v>
       </c>
@@ -73494,7 +73179,7 @@
       </c>
       <c r="AM382" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN382" t="b">
@@ -73644,9 +73329,6 @@
       <c r="P383" t="n">
         <v>8</v>
       </c>
-      <c r="Q383" t="n">
-        <v>0</v>
-      </c>
       <c r="R383" t="n">
         <v>0.006275169090412163</v>
       </c>
@@ -73896,7 +73578,7 @@
       </c>
       <c r="AM384" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN384" t="b">
@@ -74046,9 +73728,6 @@
       <c r="P385" t="n">
         <v>2</v>
       </c>
-      <c r="Q385" t="n">
-        <v>0</v>
-      </c>
       <c r="R385" t="n">
         <v>0.001568792272603041</v>
       </c>
@@ -74298,7 +73977,7 @@
       </c>
       <c r="AM386" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN386" t="b">
@@ -74989,9 +74668,6 @@
       <c r="O390" t="n">
         <v>10</v>
       </c>
-      <c r="Q390" t="n">
-        <v>0</v>
-      </c>
       <c r="R390" t="n">
         <v>0.1830937124886756</v>
       </c>
@@ -75388,9 +75064,6 @@
       <c r="P392" t="n">
         <v>4</v>
       </c>
-      <c r="Q392" t="n">
-        <v>0</v>
-      </c>
       <c r="R392" t="n">
         <v>0.003137584545206081</v>
       </c>
@@ -75640,7 +75313,7 @@
       </c>
       <c r="AM393" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN393" t="b">
@@ -75790,9 +75463,6 @@
       <c r="P394" t="n">
         <v>3</v>
       </c>
-      <c r="Q394" t="n">
-        <v>0</v>
-      </c>
       <c r="R394" t="n">
         <v>0.002353188408904561</v>
       </c>
@@ -76042,7 +75712,7 @@
       </c>
       <c r="AM395" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN395" t="b">
@@ -76192,9 +75862,6 @@
       <c r="P396" t="n">
         <v>6</v>
       </c>
-      <c r="Q396" t="n">
-        <v>0</v>
-      </c>
       <c r="R396" t="n">
         <v>0.004706376817809122</v>
       </c>
@@ -76444,7 +76111,7 @@
       </c>
       <c r="AM397" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN397" t="b">
@@ -76594,9 +76261,6 @@
       <c r="P398" t="n">
         <v>1</v>
       </c>
-      <c r="Q398" t="n">
-        <v>0</v>
-      </c>
       <c r="R398" t="n">
         <v>0.0007843961363015203</v>
       </c>
@@ -76846,7 +76510,7 @@
       </c>
       <c r="AM399" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN399" t="b">
@@ -77537,9 +77201,6 @@
       <c r="O403" t="n">
         <v>16</v>
       </c>
-      <c r="Q403" t="n">
-        <v>0</v>
-      </c>
       <c r="R403" t="n">
         <v>0.292949939981881</v>
       </c>
@@ -77936,9 +77597,6 @@
       <c r="P405" t="n">
         <v>9</v>
       </c>
-      <c r="Q405" t="n">
-        <v>0</v>
-      </c>
       <c r="R405" t="n">
         <v>0.007059565226713681</v>
       </c>
@@ -78188,7 +77846,7 @@
       </c>
       <c r="AM406" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN406" t="b">
@@ -78338,9 +77996,6 @@
       <c r="P407" t="n">
         <v>6</v>
       </c>
-      <c r="Q407" t="n">
-        <v>0</v>
-      </c>
       <c r="R407" t="n">
         <v>0.004706376817809122</v>
       </c>
@@ -78590,7 +78245,7 @@
       </c>
       <c r="AM408" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN408" t="b">
@@ -78740,9 +78395,6 @@
       <c r="P409" t="n">
         <v>5</v>
       </c>
-      <c r="Q409" t="n">
-        <v>0</v>
-      </c>
       <c r="R409" t="n">
         <v>0.003921980681507601</v>
       </c>
@@ -78992,7 +78644,7 @@
       </c>
       <c r="AM410" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN410" t="b">
@@ -79142,9 +78794,6 @@
       <c r="P411" t="n">
         <v>8</v>
       </c>
-      <c r="Q411" t="n">
-        <v>0</v>
-      </c>
       <c r="R411" t="n">
         <v>0.006275169090412163</v>
       </c>
@@ -79394,7 +79043,7 @@
       </c>
       <c r="AM412" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN412" t="b">
@@ -79544,9 +79193,6 @@
       <c r="P413" t="n">
         <v>16</v>
       </c>
-      <c r="Q413" t="n">
-        <v>0</v>
-      </c>
       <c r="R413" t="n">
         <v>0.01255033818082433</v>
       </c>
@@ -79796,7 +79442,7 @@
       </c>
       <c r="AM414" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN414" t="b">
@@ -80487,9 +80133,6 @@
       <c r="O418" t="n">
         <v>15</v>
       </c>
-      <c r="Q418" t="n">
-        <v>0</v>
-      </c>
       <c r="R418" t="n">
         <v>0.2746405687330135</v>
       </c>
@@ -80886,9 +80529,6 @@
       <c r="P420" t="n">
         <v>20</v>
       </c>
-      <c r="Q420" t="n">
-        <v>0</v>
-      </c>
       <c r="R420" t="n">
         <v>0.0156879227260304</v>
       </c>
@@ -81138,7 +80778,7 @@
       </c>
       <c r="AM421" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN421" t="b">
@@ -81288,9 +80928,6 @@
       <c r="P422" t="n">
         <v>38</v>
       </c>
-      <c r="Q422" t="n">
-        <v>0</v>
-      </c>
       <c r="R422" t="n">
         <v>0.02980705317945777</v>
       </c>
@@ -81540,7 +81177,7 @@
       </c>
       <c r="AM423" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN423" t="b">
@@ -81690,9 +81327,6 @@
       <c r="P424" t="n">
         <v>42</v>
       </c>
-      <c r="Q424" t="n">
-        <v>0</v>
-      </c>
       <c r="R424" t="n">
         <v>0.03294463772466385</v>
       </c>
@@ -81942,7 +81576,7 @@
       </c>
       <c r="AM425" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN425" t="b">
@@ -82092,9 +81726,6 @@
       <c r="P426" t="n">
         <v>28</v>
       </c>
-      <c r="Q426" t="n">
-        <v>0</v>
-      </c>
       <c r="R426" t="n">
         <v>0.02196309181644256</v>
       </c>
@@ -82344,7 +81975,7 @@
       </c>
       <c r="AM427" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN427" t="b">

--- a/diseases/d199/2010-2014.xlsx
+++ b/diseases/d199/2010-2014.xlsx
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN3" t="b">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN8" t="b">
@@ -2888,7 +2888,7 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN13" t="b">
@@ -3825,7 +3825,7 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN18" t="b">
@@ -4762,7 +4762,7 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN23" t="b">
@@ -5699,7 +5699,7 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN28" t="b">
@@ -6636,7 +6636,7 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN33" t="b">
@@ -7573,7 +7573,7 @@
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN38" t="b">
@@ -8510,7 +8510,7 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN43" t="b">
@@ -9447,7 +9447,7 @@
       </c>
       <c r="AM48" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN48" t="b">
@@ -10384,7 +10384,7 @@
       </c>
       <c r="AM53" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN53" t="b">
@@ -11321,7 +11321,7 @@
       </c>
       <c r="AM58" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN58" t="b">
@@ -12258,7 +12258,7 @@
       </c>
       <c r="AM63" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN63" t="b">
@@ -13195,7 +13195,7 @@
       </c>
       <c r="AM68" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN68" t="b">
@@ -14132,7 +14132,7 @@
       </c>
       <c r="AM73" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN73" t="b">
@@ -15069,7 +15069,7 @@
       </c>
       <c r="AM78" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN78" t="b">
@@ -16006,7 +16006,7 @@
       </c>
       <c r="AM83" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN83" t="b">
@@ -16943,7 +16943,7 @@
       </c>
       <c r="AM88" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN88" t="b">
@@ -17880,7 +17880,7 @@
       </c>
       <c r="AM93" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN93" t="b">
@@ -18817,7 +18817,7 @@
       </c>
       <c r="AM98" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN98" t="b">
@@ -19754,7 +19754,7 @@
       </c>
       <c r="AM103" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN103" t="b">
@@ -20691,7 +20691,7 @@
       </c>
       <c r="AM108" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN108" t="b">
@@ -21628,7 +21628,7 @@
       </c>
       <c r="AM113" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN113" t="b">
@@ -22565,7 +22565,7 @@
       </c>
       <c r="AM118" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN118" t="b">
@@ -23502,7 +23502,7 @@
       </c>
       <c r="AM123" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN123" t="b">
@@ -24439,7 +24439,7 @@
       </c>
       <c r="AM128" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN128" t="b">
@@ -25376,7 +25376,7 @@
       </c>
       <c r="AM133" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN133" t="b">
@@ -26313,7 +26313,7 @@
       </c>
       <c r="AM138" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN138" t="b">
@@ -27250,7 +27250,7 @@
       </c>
       <c r="AM143" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN143" t="b">
@@ -28187,7 +28187,7 @@
       </c>
       <c r="AM148" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN148" t="b">
@@ -29124,7 +29124,7 @@
       </c>
       <c r="AM153" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN153" t="b">
@@ -30061,7 +30061,7 @@
       </c>
       <c r="AM158" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN158" t="b">
@@ -30998,7 +30998,7 @@
       </c>
       <c r="AM163" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN163" t="b">
@@ -31935,7 +31935,7 @@
       </c>
       <c r="AM168" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN168" t="b">
@@ -32872,7 +32872,7 @@
       </c>
       <c r="AM173" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN173" t="b">
@@ -33809,7 +33809,7 @@
       </c>
       <c r="AM178" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN178" t="b">
@@ -34746,7 +34746,7 @@
       </c>
       <c r="AM183" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN183" t="b">
@@ -35683,7 +35683,7 @@
       </c>
       <c r="AM188" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN188" t="b">
@@ -36620,7 +36620,7 @@
       </c>
       <c r="AM193" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN193" t="b">
@@ -37557,7 +37557,7 @@
       </c>
       <c r="AM198" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN198" t="b">
@@ -38494,7 +38494,7 @@
       </c>
       <c r="AM203" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN203" t="b">
@@ -39431,7 +39431,7 @@
       </c>
       <c r="AM208" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN208" t="b">
@@ -40368,7 +40368,7 @@
       </c>
       <c r="AM213" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN213" t="b">
@@ -41305,7 +41305,7 @@
       </c>
       <c r="AM218" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN218" t="b">
@@ -42242,7 +42242,7 @@
       </c>
       <c r="AM223" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN223" t="b">
@@ -43179,7 +43179,7 @@
       </c>
       <c r="AM228" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN228" t="b">
@@ -44914,7 +44914,7 @@
       </c>
       <c r="AM237" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN237" t="b">
@@ -47447,7 +47447,7 @@
       </c>
       <c r="AM250" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN250" t="b">
@@ -50379,7 +50379,7 @@
       </c>
       <c r="AM265" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN265" t="b">
@@ -52912,7 +52912,7 @@
       </c>
       <c r="AM278" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN278" t="b">
@@ -55445,7 +55445,7 @@
       </c>
       <c r="AM291" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN291" t="b">
@@ -58377,7 +58377,7 @@
       </c>
       <c r="AM306" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN306" t="b">
@@ -60910,7 +60910,7 @@
       </c>
       <c r="AM319" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN319" t="b">
@@ -63443,7 +63443,7 @@
       </c>
       <c r="AM332" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN332" t="b">
@@ -66375,7 +66375,7 @@
       </c>
       <c r="AM347" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN347" t="b">
@@ -68908,7 +68908,7 @@
       </c>
       <c r="AM360" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN360" t="b">
@@ -71840,7 +71840,7 @@
       </c>
       <c r="AM375" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN375" t="b">
@@ -74373,7 +74373,7 @@
       </c>
       <c r="AM388" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN388" t="b">
@@ -76906,7 +76906,7 @@
       </c>
       <c r="AM401" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN401" t="b">
@@ -79838,7 +79838,7 @@
       </c>
       <c r="AM416" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN416" t="b">

--- a/diseases/d199/2010-2014.xlsx
+++ b/diseases/d199/2010-2014.xlsx
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
@@ -2878,7 +2878,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3815,7 +3815,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
@@ -4752,7 +4752,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5689,7 +5689,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
@@ -6626,7 +6626,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7563,7 +7563,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK38" t="inlineStr">
@@ -8500,7 +8500,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9437,7 +9437,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
@@ -10374,7 +10374,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -11311,7 +11311,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK58" t="inlineStr">
@@ -12248,7 +12248,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13185,7 +13185,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK68" t="inlineStr">
@@ -14122,7 +14122,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -15059,7 +15059,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
@@ -15996,7 +15996,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -16933,7 +16933,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK88" t="inlineStr">
@@ -17870,7 +17870,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -18807,7 +18807,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK98" t="inlineStr">
@@ -19744,7 +19744,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -20681,7 +20681,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK108" t="inlineStr">
@@ -21618,7 +21618,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -22555,7 +22555,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK118" t="inlineStr">
@@ -23492,7 +23492,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -24429,7 +24429,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK128" t="inlineStr">
@@ -25366,7 +25366,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
@@ -26303,7 +26303,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK138" t="inlineStr">
@@ -27240,7 +27240,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK143" t="inlineStr">
@@ -28177,7 +28177,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK148" t="inlineStr">
@@ -29114,7 +29114,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -30051,7 +30051,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK158" t="inlineStr">
@@ -30988,7 +30988,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK163" t="inlineStr">
@@ -31925,7 +31925,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK168" t="inlineStr">
@@ -32862,7 +32862,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK173" t="inlineStr">
@@ -33799,7 +33799,7 @@
       </c>
       <c r="AJ178" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK178" t="inlineStr">
@@ -34736,7 +34736,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK183" t="inlineStr">
@@ -35673,7 +35673,7 @@
       </c>
       <c r="AJ188" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK188" t="inlineStr">
@@ -36610,7 +36610,7 @@
       </c>
       <c r="AJ193" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK193" t="inlineStr">
@@ -37547,7 +37547,7 @@
       </c>
       <c r="AJ198" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK198" t="inlineStr">
@@ -38484,7 +38484,7 @@
       </c>
       <c r="AJ203" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK203" t="inlineStr">
@@ -39421,7 +39421,7 @@
       </c>
       <c r="AJ208" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK208" t="inlineStr">
@@ -40358,7 +40358,7 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK213" t="inlineStr">
@@ -41295,7 +41295,7 @@
       </c>
       <c r="AJ218" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK218" t="inlineStr">
@@ -42232,7 +42232,7 @@
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK223" t="inlineStr">
@@ -43169,7 +43169,7 @@
       </c>
       <c r="AJ228" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK228" t="inlineStr">
@@ -44109,7 +44109,7 @@
       </c>
       <c r="AJ233" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK233" t="inlineStr">
@@ -44508,7 +44508,7 @@
       </c>
       <c r="AJ235" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK235" t="inlineStr">
@@ -44904,7 +44904,7 @@
       </c>
       <c r="AJ237" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK237" t="inlineStr">
@@ -45844,7 +45844,7 @@
       </c>
       <c r="AJ242" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK242" t="inlineStr">
@@ -46243,7 +46243,7 @@
       </c>
       <c r="AJ244" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK244" t="inlineStr">
@@ -46642,7 +46642,7 @@
       </c>
       <c r="AJ246" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK246" t="inlineStr">
@@ -47041,7 +47041,7 @@
       </c>
       <c r="AJ248" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK248" t="inlineStr">
@@ -47437,7 +47437,7 @@
       </c>
       <c r="AJ250" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK250" t="inlineStr">
@@ -48377,7 +48377,7 @@
       </c>
       <c r="AJ255" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK255" t="inlineStr">
@@ -48776,7 +48776,7 @@
       </c>
       <c r="AJ257" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK257" t="inlineStr">
@@ -49175,7 +49175,7 @@
       </c>
       <c r="AJ259" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK259" t="inlineStr">
@@ -49574,7 +49574,7 @@
       </c>
       <c r="AJ261" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK261" t="inlineStr">
@@ -49973,7 +49973,7 @@
       </c>
       <c r="AJ263" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK263" t="inlineStr">
@@ -50369,7 +50369,7 @@
       </c>
       <c r="AJ265" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK265" t="inlineStr">
@@ -51309,7 +51309,7 @@
       </c>
       <c r="AJ270" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK270" t="inlineStr">
@@ -51708,7 +51708,7 @@
       </c>
       <c r="AJ272" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK272" t="inlineStr">
@@ -52107,7 +52107,7 @@
       </c>
       <c r="AJ274" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK274" t="inlineStr">
@@ -52506,7 +52506,7 @@
       </c>
       <c r="AJ276" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK276" t="inlineStr">
@@ -52902,7 +52902,7 @@
       </c>
       <c r="AJ278" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK278" t="inlineStr">
@@ -53842,7 +53842,7 @@
       </c>
       <c r="AJ283" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK283" t="inlineStr">
@@ -54241,7 +54241,7 @@
       </c>
       <c r="AJ285" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK285" t="inlineStr">
@@ -54640,7 +54640,7 @@
       </c>
       <c r="AJ287" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK287" t="inlineStr">
@@ -55039,7 +55039,7 @@
       </c>
       <c r="AJ289" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK289" t="inlineStr">
@@ -55435,7 +55435,7 @@
       </c>
       <c r="AJ291" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK291" t="inlineStr">
@@ -56375,7 +56375,7 @@
       </c>
       <c r="AJ296" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK296" t="inlineStr">
@@ -56774,7 +56774,7 @@
       </c>
       <c r="AJ298" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK298" t="inlineStr">
@@ -57173,7 +57173,7 @@
       </c>
       <c r="AJ300" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK300" t="inlineStr">
@@ -57572,7 +57572,7 @@
       </c>
       <c r="AJ302" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK302" t="inlineStr">
@@ -57971,7 +57971,7 @@
       </c>
       <c r="AJ304" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK304" t="inlineStr">
@@ -58367,7 +58367,7 @@
       </c>
       <c r="AJ306" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK306" t="inlineStr">
@@ -59307,7 +59307,7 @@
       </c>
       <c r="AJ311" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK311" t="inlineStr">
@@ -59706,7 +59706,7 @@
       </c>
       <c r="AJ313" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK313" t="inlineStr">
@@ -60105,7 +60105,7 @@
       </c>
       <c r="AJ315" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK315" t="inlineStr">
@@ -60504,7 +60504,7 @@
       </c>
       <c r="AJ317" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK317" t="inlineStr">
@@ -60900,7 +60900,7 @@
       </c>
       <c r="AJ319" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK319" t="inlineStr">
@@ -61840,7 +61840,7 @@
       </c>
       <c r="AJ324" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK324" t="inlineStr">
@@ -62239,7 +62239,7 @@
       </c>
       <c r="AJ326" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK326" t="inlineStr">
@@ -62638,7 +62638,7 @@
       </c>
       <c r="AJ328" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK328" t="inlineStr">
@@ -63037,7 +63037,7 @@
       </c>
       <c r="AJ330" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK330" t="inlineStr">
@@ -63433,7 +63433,7 @@
       </c>
       <c r="AJ332" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK332" t="inlineStr">
@@ -64373,7 +64373,7 @@
       </c>
       <c r="AJ337" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK337" t="inlineStr">
@@ -64772,7 +64772,7 @@
       </c>
       <c r="AJ339" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK339" t="inlineStr">
@@ -65171,7 +65171,7 @@
       </c>
       <c r="AJ341" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK341" t="inlineStr">
@@ -65570,7 +65570,7 @@
       </c>
       <c r="AJ343" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK343" t="inlineStr">
@@ -65969,7 +65969,7 @@
       </c>
       <c r="AJ345" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK345" t="inlineStr">
@@ -66365,7 +66365,7 @@
       </c>
       <c r="AJ347" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK347" t="inlineStr">
@@ -67305,7 +67305,7 @@
       </c>
       <c r="AJ352" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK352" t="inlineStr">
@@ -67704,7 +67704,7 @@
       </c>
       <c r="AJ354" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK354" t="inlineStr">
@@ -68103,7 +68103,7 @@
       </c>
       <c r="AJ356" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK356" t="inlineStr">
@@ -68502,7 +68502,7 @@
       </c>
       <c r="AJ358" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK358" t="inlineStr">
@@ -68898,7 +68898,7 @@
       </c>
       <c r="AJ360" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK360" t="inlineStr">
@@ -69838,7 +69838,7 @@
       </c>
       <c r="AJ365" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK365" t="inlineStr">
@@ -70237,7 +70237,7 @@
       </c>
       <c r="AJ367" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK367" t="inlineStr">
@@ -70636,7 +70636,7 @@
       </c>
       <c r="AJ369" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK369" t="inlineStr">
@@ -71035,7 +71035,7 @@
       </c>
       <c r="AJ371" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK371" t="inlineStr">
@@ -71434,7 +71434,7 @@
       </c>
       <c r="AJ373" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK373" t="inlineStr">
@@ -71830,7 +71830,7 @@
       </c>
       <c r="AJ375" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK375" t="inlineStr">
@@ -72770,7 +72770,7 @@
       </c>
       <c r="AJ380" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK380" t="inlineStr">
@@ -73169,7 +73169,7 @@
       </c>
       <c r="AJ382" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK382" t="inlineStr">
@@ -73568,7 +73568,7 @@
       </c>
       <c r="AJ384" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK384" t="inlineStr">
@@ -73967,7 +73967,7 @@
       </c>
       <c r="AJ386" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK386" t="inlineStr">
@@ -74363,7 +74363,7 @@
       </c>
       <c r="AJ388" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK388" t="inlineStr">
@@ -75303,7 +75303,7 @@
       </c>
       <c r="AJ393" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK393" t="inlineStr">
@@ -75702,7 +75702,7 @@
       </c>
       <c r="AJ395" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK395" t="inlineStr">
@@ -76101,7 +76101,7 @@
       </c>
       <c r="AJ397" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK397" t="inlineStr">
@@ -76500,7 +76500,7 @@
       </c>
       <c r="AJ399" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK399" t="inlineStr">
@@ -76896,7 +76896,7 @@
       </c>
       <c r="AJ401" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK401" t="inlineStr">
@@ -77836,7 +77836,7 @@
       </c>
       <c r="AJ406" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK406" t="inlineStr">
@@ -78235,7 +78235,7 @@
       </c>
       <c r="AJ408" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK408" t="inlineStr">
@@ -78634,7 +78634,7 @@
       </c>
       <c r="AJ410" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK410" t="inlineStr">
@@ -79033,7 +79033,7 @@
       </c>
       <c r="AJ412" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK412" t="inlineStr">
@@ -79432,7 +79432,7 @@
       </c>
       <c r="AJ414" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK414" t="inlineStr">
@@ -79828,7 +79828,7 @@
       </c>
       <c r="AJ416" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK416" t="inlineStr">
@@ -80768,7 +80768,7 @@
       </c>
       <c r="AJ421" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK421" t="inlineStr">
@@ -81167,7 +81167,7 @@
       </c>
       <c r="AJ423" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK423" t="inlineStr">
@@ -81566,7 +81566,7 @@
       </c>
       <c r="AJ425" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK425" t="inlineStr">
@@ -81965,7 +81965,7 @@
       </c>
       <c r="AJ427" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK427" t="inlineStr">

--- a/diseases/d199/2010-2014.xlsx
+++ b/diseases/d199/2010-2014.xlsx
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
@@ -2878,7 +2878,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3815,7 +3815,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
@@ -4752,7 +4752,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5689,7 +5689,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
@@ -6626,7 +6626,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7563,7 +7563,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK38" t="inlineStr">
@@ -8500,7 +8500,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9437,7 +9437,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
@@ -10374,7 +10374,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -11311,7 +11311,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK58" t="inlineStr">
@@ -12248,7 +12248,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13185,7 +13185,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK68" t="inlineStr">
@@ -14122,7 +14122,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -15059,7 +15059,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
@@ -15996,7 +15996,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -16933,7 +16933,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK88" t="inlineStr">
@@ -17870,7 +17870,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -18807,7 +18807,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK98" t="inlineStr">
@@ -19744,7 +19744,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -20681,7 +20681,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK108" t="inlineStr">
@@ -21618,7 +21618,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -22555,7 +22555,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK118" t="inlineStr">
@@ -23492,7 +23492,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -24429,7 +24429,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK128" t="inlineStr">
@@ -25366,7 +25366,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
@@ -26303,7 +26303,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK138" t="inlineStr">
@@ -27240,7 +27240,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK143" t="inlineStr">
@@ -28177,7 +28177,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK148" t="inlineStr">
@@ -29114,7 +29114,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -30051,7 +30051,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK158" t="inlineStr">
@@ -30988,7 +30988,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK163" t="inlineStr">
@@ -31925,7 +31925,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK168" t="inlineStr">
@@ -32862,7 +32862,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK173" t="inlineStr">
@@ -33799,7 +33799,7 @@
       </c>
       <c r="AJ178" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK178" t="inlineStr">
@@ -34736,7 +34736,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK183" t="inlineStr">
@@ -35673,7 +35673,7 @@
       </c>
       <c r="AJ188" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK188" t="inlineStr">
@@ -36610,7 +36610,7 @@
       </c>
       <c r="AJ193" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK193" t="inlineStr">
@@ -37547,7 +37547,7 @@
       </c>
       <c r="AJ198" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK198" t="inlineStr">
@@ -38484,7 +38484,7 @@
       </c>
       <c r="AJ203" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK203" t="inlineStr">
@@ -39421,7 +39421,7 @@
       </c>
       <c r="AJ208" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK208" t="inlineStr">
@@ -40358,7 +40358,7 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK213" t="inlineStr">
@@ -41295,7 +41295,7 @@
       </c>
       <c r="AJ218" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK218" t="inlineStr">
@@ -42232,7 +42232,7 @@
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK223" t="inlineStr">
@@ -43169,7 +43169,7 @@
       </c>
       <c r="AJ228" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK228" t="inlineStr">
@@ -44109,7 +44109,7 @@
       </c>
       <c r="AJ233" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK233" t="inlineStr">
@@ -44508,7 +44508,7 @@
       </c>
       <c r="AJ235" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK235" t="inlineStr">
@@ -44904,7 +44904,7 @@
       </c>
       <c r="AJ237" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK237" t="inlineStr">
@@ -45844,7 +45844,7 @@
       </c>
       <c r="AJ242" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK242" t="inlineStr">
@@ -46243,7 +46243,7 @@
       </c>
       <c r="AJ244" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK244" t="inlineStr">
@@ -46642,7 +46642,7 @@
       </c>
       <c r="AJ246" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK246" t="inlineStr">
@@ -47041,7 +47041,7 @@
       </c>
       <c r="AJ248" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK248" t="inlineStr">
@@ -47437,7 +47437,7 @@
       </c>
       <c r="AJ250" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK250" t="inlineStr">
@@ -48377,7 +48377,7 @@
       </c>
       <c r="AJ255" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK255" t="inlineStr">
@@ -48776,7 +48776,7 @@
       </c>
       <c r="AJ257" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK257" t="inlineStr">
@@ -49175,7 +49175,7 @@
       </c>
       <c r="AJ259" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK259" t="inlineStr">
@@ -49574,7 +49574,7 @@
       </c>
       <c r="AJ261" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK261" t="inlineStr">
@@ -49973,7 +49973,7 @@
       </c>
       <c r="AJ263" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK263" t="inlineStr">
@@ -50369,7 +50369,7 @@
       </c>
       <c r="AJ265" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK265" t="inlineStr">
@@ -51309,7 +51309,7 @@
       </c>
       <c r="AJ270" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK270" t="inlineStr">
@@ -51708,7 +51708,7 @@
       </c>
       <c r="AJ272" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK272" t="inlineStr">
@@ -52107,7 +52107,7 @@
       </c>
       <c r="AJ274" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK274" t="inlineStr">
@@ -52506,7 +52506,7 @@
       </c>
       <c r="AJ276" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK276" t="inlineStr">
@@ -52902,7 +52902,7 @@
       </c>
       <c r="AJ278" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK278" t="inlineStr">
@@ -53842,7 +53842,7 @@
       </c>
       <c r="AJ283" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK283" t="inlineStr">
@@ -54241,7 +54241,7 @@
       </c>
       <c r="AJ285" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK285" t="inlineStr">
@@ -54640,7 +54640,7 @@
       </c>
       <c r="AJ287" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK287" t="inlineStr">
@@ -55039,7 +55039,7 @@
       </c>
       <c r="AJ289" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK289" t="inlineStr">
@@ -55435,7 +55435,7 @@
       </c>
       <c r="AJ291" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK291" t="inlineStr">
@@ -56375,7 +56375,7 @@
       </c>
       <c r="AJ296" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK296" t="inlineStr">
@@ -56774,7 +56774,7 @@
       </c>
       <c r="AJ298" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK298" t="inlineStr">
@@ -57173,7 +57173,7 @@
       </c>
       <c r="AJ300" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK300" t="inlineStr">
@@ -57572,7 +57572,7 @@
       </c>
       <c r="AJ302" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK302" t="inlineStr">
@@ -57971,7 +57971,7 @@
       </c>
       <c r="AJ304" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK304" t="inlineStr">
@@ -58367,7 +58367,7 @@
       </c>
       <c r="AJ306" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK306" t="inlineStr">
@@ -59307,7 +59307,7 @@
       </c>
       <c r="AJ311" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK311" t="inlineStr">
@@ -59706,7 +59706,7 @@
       </c>
       <c r="AJ313" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK313" t="inlineStr">
@@ -60105,7 +60105,7 @@
       </c>
       <c r="AJ315" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK315" t="inlineStr">
@@ -60504,7 +60504,7 @@
       </c>
       <c r="AJ317" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK317" t="inlineStr">
@@ -60900,7 +60900,7 @@
       </c>
       <c r="AJ319" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK319" t="inlineStr">
@@ -61840,7 +61840,7 @@
       </c>
       <c r="AJ324" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK324" t="inlineStr">
@@ -62239,7 +62239,7 @@
       </c>
       <c r="AJ326" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK326" t="inlineStr">
@@ -62638,7 +62638,7 @@
       </c>
       <c r="AJ328" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK328" t="inlineStr">
@@ -63037,7 +63037,7 @@
       </c>
       <c r="AJ330" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK330" t="inlineStr">
@@ -63433,7 +63433,7 @@
       </c>
       <c r="AJ332" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK332" t="inlineStr">
@@ -64373,7 +64373,7 @@
       </c>
       <c r="AJ337" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK337" t="inlineStr">
@@ -64772,7 +64772,7 @@
       </c>
       <c r="AJ339" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK339" t="inlineStr">
@@ -65171,7 +65171,7 @@
       </c>
       <c r="AJ341" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK341" t="inlineStr">
@@ -65570,7 +65570,7 @@
       </c>
       <c r="AJ343" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK343" t="inlineStr">
@@ -65969,7 +65969,7 @@
       </c>
       <c r="AJ345" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK345" t="inlineStr">
@@ -66365,7 +66365,7 @@
       </c>
       <c r="AJ347" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK347" t="inlineStr">
@@ -67305,7 +67305,7 @@
       </c>
       <c r="AJ352" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK352" t="inlineStr">
@@ -67704,7 +67704,7 @@
       </c>
       <c r="AJ354" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK354" t="inlineStr">
@@ -68103,7 +68103,7 @@
       </c>
       <c r="AJ356" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK356" t="inlineStr">
@@ -68502,7 +68502,7 @@
       </c>
       <c r="AJ358" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK358" t="inlineStr">
@@ -68898,7 +68898,7 @@
       </c>
       <c r="AJ360" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK360" t="inlineStr">
@@ -69838,7 +69838,7 @@
       </c>
       <c r="AJ365" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK365" t="inlineStr">
@@ -70237,7 +70237,7 @@
       </c>
       <c r="AJ367" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK367" t="inlineStr">
@@ -70636,7 +70636,7 @@
       </c>
       <c r="AJ369" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK369" t="inlineStr">
@@ -71035,7 +71035,7 @@
       </c>
       <c r="AJ371" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK371" t="inlineStr">
@@ -71434,7 +71434,7 @@
       </c>
       <c r="AJ373" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK373" t="inlineStr">
@@ -71830,7 +71830,7 @@
       </c>
       <c r="AJ375" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK375" t="inlineStr">
@@ -72770,7 +72770,7 @@
       </c>
       <c r="AJ380" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK380" t="inlineStr">
@@ -73169,7 +73169,7 @@
       </c>
       <c r="AJ382" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK382" t="inlineStr">
@@ -73568,7 +73568,7 @@
       </c>
       <c r="AJ384" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK384" t="inlineStr">
@@ -73967,7 +73967,7 @@
       </c>
       <c r="AJ386" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK386" t="inlineStr">
@@ -74363,7 +74363,7 @@
       </c>
       <c r="AJ388" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK388" t="inlineStr">
@@ -75303,7 +75303,7 @@
       </c>
       <c r="AJ393" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK393" t="inlineStr">
@@ -75702,7 +75702,7 @@
       </c>
       <c r="AJ395" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK395" t="inlineStr">
@@ -76101,7 +76101,7 @@
       </c>
       <c r="AJ397" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK397" t="inlineStr">
@@ -76500,7 +76500,7 @@
       </c>
       <c r="AJ399" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK399" t="inlineStr">
@@ -76896,7 +76896,7 @@
       </c>
       <c r="AJ401" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK401" t="inlineStr">
@@ -77836,7 +77836,7 @@
       </c>
       <c r="AJ406" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK406" t="inlineStr">
@@ -78235,7 +78235,7 @@
       </c>
       <c r="AJ408" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK408" t="inlineStr">
@@ -78634,7 +78634,7 @@
       </c>
       <c r="AJ410" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK410" t="inlineStr">
@@ -79033,7 +79033,7 @@
       </c>
       <c r="AJ412" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK412" t="inlineStr">
@@ -79432,7 +79432,7 @@
       </c>
       <c r="AJ414" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK414" t="inlineStr">
@@ -79828,7 +79828,7 @@
       </c>
       <c r="AJ416" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK416" t="inlineStr">
@@ -80768,7 +80768,7 @@
       </c>
       <c r="AJ421" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK421" t="inlineStr">
@@ -81167,7 +81167,7 @@
       </c>
       <c r="AJ423" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK423" t="inlineStr">
@@ -81566,7 +81566,7 @@
       </c>
       <c r="AJ425" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK425" t="inlineStr">
@@ -81965,7 +81965,7 @@
       </c>
       <c r="AJ427" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK427" t="inlineStr">

--- a/diseases/d199/2010-2014.xlsx
+++ b/diseases/d199/2010-2014.xlsx
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
@@ -2878,7 +2878,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3815,7 +3815,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
@@ -4752,7 +4752,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5689,7 +5689,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
@@ -6626,7 +6626,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7563,7 +7563,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK38" t="inlineStr">
@@ -8500,7 +8500,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9437,7 +9437,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
@@ -10374,7 +10374,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -11311,7 +11311,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK58" t="inlineStr">
@@ -12248,7 +12248,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13185,7 +13185,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK68" t="inlineStr">
@@ -14122,7 +14122,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -15059,7 +15059,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
@@ -15996,7 +15996,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -16933,7 +16933,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK88" t="inlineStr">
@@ -17870,7 +17870,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -18807,7 +18807,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK98" t="inlineStr">
@@ -19744,7 +19744,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -20681,7 +20681,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK108" t="inlineStr">
@@ -21618,7 +21618,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -22555,7 +22555,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK118" t="inlineStr">
@@ -23492,7 +23492,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -24429,7 +24429,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK128" t="inlineStr">
@@ -25366,7 +25366,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
@@ -26303,7 +26303,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK138" t="inlineStr">
@@ -27240,7 +27240,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK143" t="inlineStr">
@@ -28177,7 +28177,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK148" t="inlineStr">
@@ -29114,7 +29114,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -30051,7 +30051,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK158" t="inlineStr">
@@ -30988,7 +30988,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK163" t="inlineStr">
@@ -31925,7 +31925,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK168" t="inlineStr">
@@ -32862,7 +32862,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK173" t="inlineStr">
@@ -33799,7 +33799,7 @@
       </c>
       <c r="AJ178" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK178" t="inlineStr">
@@ -34736,7 +34736,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK183" t="inlineStr">
@@ -35673,7 +35673,7 @@
       </c>
       <c r="AJ188" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK188" t="inlineStr">
@@ -36610,7 +36610,7 @@
       </c>
       <c r="AJ193" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK193" t="inlineStr">
@@ -37547,7 +37547,7 @@
       </c>
       <c r="AJ198" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK198" t="inlineStr">
@@ -38484,7 +38484,7 @@
       </c>
       <c r="AJ203" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK203" t="inlineStr">
@@ -39421,7 +39421,7 @@
       </c>
       <c r="AJ208" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK208" t="inlineStr">
@@ -40358,7 +40358,7 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK213" t="inlineStr">
@@ -41295,7 +41295,7 @@
       </c>
       <c r="AJ218" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK218" t="inlineStr">
@@ -42232,7 +42232,7 @@
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK223" t="inlineStr">
@@ -43169,7 +43169,7 @@
       </c>
       <c r="AJ228" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK228" t="inlineStr">
@@ -44109,7 +44109,7 @@
       </c>
       <c r="AJ233" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK233" t="inlineStr">
@@ -44508,7 +44508,7 @@
       </c>
       <c r="AJ235" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK235" t="inlineStr">
@@ -44904,7 +44904,7 @@
       </c>
       <c r="AJ237" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK237" t="inlineStr">
@@ -45844,7 +45844,7 @@
       </c>
       <c r="AJ242" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK242" t="inlineStr">
@@ -46243,7 +46243,7 @@
       </c>
       <c r="AJ244" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK244" t="inlineStr">
@@ -46642,7 +46642,7 @@
       </c>
       <c r="AJ246" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK246" t="inlineStr">
@@ -47041,7 +47041,7 @@
       </c>
       <c r="AJ248" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK248" t="inlineStr">
@@ -47437,7 +47437,7 @@
       </c>
       <c r="AJ250" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK250" t="inlineStr">
@@ -48377,7 +48377,7 @@
       </c>
       <c r="AJ255" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK255" t="inlineStr">
@@ -48776,7 +48776,7 @@
       </c>
       <c r="AJ257" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK257" t="inlineStr">
@@ -49175,7 +49175,7 @@
       </c>
       <c r="AJ259" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK259" t="inlineStr">
@@ -49574,7 +49574,7 @@
       </c>
       <c r="AJ261" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK261" t="inlineStr">
@@ -49973,7 +49973,7 @@
       </c>
       <c r="AJ263" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK263" t="inlineStr">
@@ -50369,7 +50369,7 @@
       </c>
       <c r="AJ265" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK265" t="inlineStr">
@@ -51309,7 +51309,7 @@
       </c>
       <c r="AJ270" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK270" t="inlineStr">
@@ -51708,7 +51708,7 @@
       </c>
       <c r="AJ272" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK272" t="inlineStr">
@@ -52107,7 +52107,7 @@
       </c>
       <c r="AJ274" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK274" t="inlineStr">
@@ -52506,7 +52506,7 @@
       </c>
       <c r="AJ276" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK276" t="inlineStr">
@@ -52902,7 +52902,7 @@
       </c>
       <c r="AJ278" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK278" t="inlineStr">
@@ -53842,7 +53842,7 @@
       </c>
       <c r="AJ283" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK283" t="inlineStr">
@@ -54241,7 +54241,7 @@
       </c>
       <c r="AJ285" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK285" t="inlineStr">
@@ -54640,7 +54640,7 @@
       </c>
       <c r="AJ287" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK287" t="inlineStr">
@@ -55039,7 +55039,7 @@
       </c>
       <c r="AJ289" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK289" t="inlineStr">
@@ -55435,7 +55435,7 @@
       </c>
       <c r="AJ291" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK291" t="inlineStr">
@@ -56375,7 +56375,7 @@
       </c>
       <c r="AJ296" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK296" t="inlineStr">
@@ -56774,7 +56774,7 @@
       </c>
       <c r="AJ298" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK298" t="inlineStr">
@@ -57173,7 +57173,7 @@
       </c>
       <c r="AJ300" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK300" t="inlineStr">
@@ -57572,7 +57572,7 @@
       </c>
       <c r="AJ302" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK302" t="inlineStr">
@@ -57971,7 +57971,7 @@
       </c>
       <c r="AJ304" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK304" t="inlineStr">
@@ -58367,7 +58367,7 @@
       </c>
       <c r="AJ306" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK306" t="inlineStr">
@@ -59307,7 +59307,7 @@
       </c>
       <c r="AJ311" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK311" t="inlineStr">
@@ -59706,7 +59706,7 @@
       </c>
       <c r="AJ313" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK313" t="inlineStr">
@@ -60105,7 +60105,7 @@
       </c>
       <c r="AJ315" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK315" t="inlineStr">
@@ -60504,7 +60504,7 @@
       </c>
       <c r="AJ317" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK317" t="inlineStr">
@@ -60900,7 +60900,7 @@
       </c>
       <c r="AJ319" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK319" t="inlineStr">
@@ -61840,7 +61840,7 @@
       </c>
       <c r="AJ324" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK324" t="inlineStr">
@@ -62239,7 +62239,7 @@
       </c>
       <c r="AJ326" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK326" t="inlineStr">
@@ -62638,7 +62638,7 @@
       </c>
       <c r="AJ328" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK328" t="inlineStr">
@@ -63037,7 +63037,7 @@
       </c>
       <c r="AJ330" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK330" t="inlineStr">
@@ -63433,7 +63433,7 @@
       </c>
       <c r="AJ332" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK332" t="inlineStr">
@@ -64373,7 +64373,7 @@
       </c>
       <c r="AJ337" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK337" t="inlineStr">
@@ -64772,7 +64772,7 @@
       </c>
       <c r="AJ339" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK339" t="inlineStr">
@@ -65171,7 +65171,7 @@
       </c>
       <c r="AJ341" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK341" t="inlineStr">
@@ -65570,7 +65570,7 @@
       </c>
       <c r="AJ343" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK343" t="inlineStr">
@@ -65969,7 +65969,7 @@
       </c>
       <c r="AJ345" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK345" t="inlineStr">
@@ -66365,7 +66365,7 @@
       </c>
       <c r="AJ347" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK347" t="inlineStr">
@@ -67305,7 +67305,7 @@
       </c>
       <c r="AJ352" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK352" t="inlineStr">
@@ -67704,7 +67704,7 @@
       </c>
       <c r="AJ354" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK354" t="inlineStr">
@@ -68103,7 +68103,7 @@
       </c>
       <c r="AJ356" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK356" t="inlineStr">
@@ -68502,7 +68502,7 @@
       </c>
       <c r="AJ358" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK358" t="inlineStr">
@@ -68898,7 +68898,7 @@
       </c>
       <c r="AJ360" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK360" t="inlineStr">
@@ -69838,7 +69838,7 @@
       </c>
       <c r="AJ365" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK365" t="inlineStr">
@@ -70237,7 +70237,7 @@
       </c>
       <c r="AJ367" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK367" t="inlineStr">
@@ -70636,7 +70636,7 @@
       </c>
       <c r="AJ369" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK369" t="inlineStr">
@@ -71035,7 +71035,7 @@
       </c>
       <c r="AJ371" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK371" t="inlineStr">
@@ -71434,7 +71434,7 @@
       </c>
       <c r="AJ373" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK373" t="inlineStr">
@@ -71830,7 +71830,7 @@
       </c>
       <c r="AJ375" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK375" t="inlineStr">
@@ -72770,7 +72770,7 @@
       </c>
       <c r="AJ380" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK380" t="inlineStr">
@@ -73169,7 +73169,7 @@
       </c>
       <c r="AJ382" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK382" t="inlineStr">
@@ -73568,7 +73568,7 @@
       </c>
       <c r="AJ384" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK384" t="inlineStr">
@@ -73967,7 +73967,7 @@
       </c>
       <c r="AJ386" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK386" t="inlineStr">
@@ -74363,7 +74363,7 @@
       </c>
       <c r="AJ388" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK388" t="inlineStr">
@@ -75303,7 +75303,7 @@
       </c>
       <c r="AJ393" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK393" t="inlineStr">
@@ -75702,7 +75702,7 @@
       </c>
       <c r="AJ395" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK395" t="inlineStr">
@@ -76101,7 +76101,7 @@
       </c>
       <c r="AJ397" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK397" t="inlineStr">
@@ -76500,7 +76500,7 @@
       </c>
       <c r="AJ399" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK399" t="inlineStr">
@@ -76896,7 +76896,7 @@
       </c>
       <c r="AJ401" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK401" t="inlineStr">
@@ -77836,7 +77836,7 @@
       </c>
       <c r="AJ406" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK406" t="inlineStr">
@@ -78235,7 +78235,7 @@
       </c>
       <c r="AJ408" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK408" t="inlineStr">
@@ -78634,7 +78634,7 @@
       </c>
       <c r="AJ410" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK410" t="inlineStr">
@@ -79033,7 +79033,7 @@
       </c>
       <c r="AJ412" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK412" t="inlineStr">
@@ -79432,7 +79432,7 @@
       </c>
       <c r="AJ414" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK414" t="inlineStr">
@@ -79828,7 +79828,7 @@
       </c>
       <c r="AJ416" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK416" t="inlineStr">
@@ -80768,7 +80768,7 @@
       </c>
       <c r="AJ421" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK421" t="inlineStr">
@@ -81167,7 +81167,7 @@
       </c>
       <c r="AJ423" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK423" t="inlineStr">
@@ -81566,7 +81566,7 @@
       </c>
       <c r="AJ425" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK425" t="inlineStr">
@@ -81965,7 +81965,7 @@
       </c>
       <c r="AJ427" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK427" t="inlineStr">

--- a/diseases/d199/2010-2014.xlsx
+++ b/diseases/d199/2010-2014.xlsx
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
@@ -2878,7 +2878,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3815,7 +3815,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
@@ -4752,7 +4752,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5689,7 +5689,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
@@ -6626,7 +6626,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7563,7 +7563,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK38" t="inlineStr">
@@ -8500,7 +8500,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9437,7 +9437,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
@@ -10374,7 +10374,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -11311,7 +11311,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK58" t="inlineStr">
@@ -12248,7 +12248,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13185,7 +13185,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK68" t="inlineStr">
@@ -14122,7 +14122,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -15059,7 +15059,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
@@ -15996,7 +15996,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -16933,7 +16933,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK88" t="inlineStr">
@@ -17870,7 +17870,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -18807,7 +18807,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK98" t="inlineStr">
@@ -19744,7 +19744,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -20681,7 +20681,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK108" t="inlineStr">
@@ -21618,7 +21618,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -22555,7 +22555,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK118" t="inlineStr">
@@ -23492,7 +23492,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -24429,7 +24429,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK128" t="inlineStr">
@@ -25366,7 +25366,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
@@ -26303,7 +26303,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK138" t="inlineStr">
@@ -27240,7 +27240,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK143" t="inlineStr">
@@ -28177,7 +28177,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK148" t="inlineStr">
@@ -29114,7 +29114,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -30051,7 +30051,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK158" t="inlineStr">
@@ -30988,7 +30988,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK163" t="inlineStr">
@@ -31925,7 +31925,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK168" t="inlineStr">
@@ -32862,7 +32862,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK173" t="inlineStr">
@@ -33799,7 +33799,7 @@
       </c>
       <c r="AJ178" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK178" t="inlineStr">
@@ -34736,7 +34736,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK183" t="inlineStr">
@@ -35673,7 +35673,7 @@
       </c>
       <c r="AJ188" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK188" t="inlineStr">
@@ -36610,7 +36610,7 @@
       </c>
       <c r="AJ193" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK193" t="inlineStr">
@@ -37547,7 +37547,7 @@
       </c>
       <c r="AJ198" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK198" t="inlineStr">
@@ -38484,7 +38484,7 @@
       </c>
       <c r="AJ203" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK203" t="inlineStr">
@@ -39421,7 +39421,7 @@
       </c>
       <c r="AJ208" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK208" t="inlineStr">
@@ -40358,7 +40358,7 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK213" t="inlineStr">
@@ -41295,7 +41295,7 @@
       </c>
       <c r="AJ218" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK218" t="inlineStr">
@@ -42232,7 +42232,7 @@
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK223" t="inlineStr">
@@ -43169,7 +43169,7 @@
       </c>
       <c r="AJ228" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK228" t="inlineStr">
@@ -44109,7 +44109,7 @@
       </c>
       <c r="AJ233" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK233" t="inlineStr">
@@ -44508,7 +44508,7 @@
       </c>
       <c r="AJ235" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK235" t="inlineStr">
@@ -44904,7 +44904,7 @@
       </c>
       <c r="AJ237" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK237" t="inlineStr">
@@ -45844,7 +45844,7 @@
       </c>
       <c r="AJ242" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK242" t="inlineStr">
@@ -46243,7 +46243,7 @@
       </c>
       <c r="AJ244" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK244" t="inlineStr">
@@ -46642,7 +46642,7 @@
       </c>
       <c r="AJ246" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK246" t="inlineStr">
@@ -47041,7 +47041,7 @@
       </c>
       <c r="AJ248" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK248" t="inlineStr">
@@ -47437,7 +47437,7 @@
       </c>
       <c r="AJ250" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK250" t="inlineStr">
@@ -48377,7 +48377,7 @@
       </c>
       <c r="AJ255" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK255" t="inlineStr">
@@ -48776,7 +48776,7 @@
       </c>
       <c r="AJ257" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK257" t="inlineStr">
@@ -49175,7 +49175,7 @@
       </c>
       <c r="AJ259" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK259" t="inlineStr">
@@ -49574,7 +49574,7 @@
       </c>
       <c r="AJ261" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK261" t="inlineStr">
@@ -49973,7 +49973,7 @@
       </c>
       <c r="AJ263" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK263" t="inlineStr">
@@ -50369,7 +50369,7 @@
       </c>
       <c r="AJ265" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK265" t="inlineStr">
@@ -51309,7 +51309,7 @@
       </c>
       <c r="AJ270" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK270" t="inlineStr">
@@ -51708,7 +51708,7 @@
       </c>
       <c r="AJ272" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK272" t="inlineStr">
@@ -52107,7 +52107,7 @@
       </c>
       <c r="AJ274" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK274" t="inlineStr">
@@ -52506,7 +52506,7 @@
       </c>
       <c r="AJ276" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK276" t="inlineStr">
@@ -52902,7 +52902,7 @@
       </c>
       <c r="AJ278" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK278" t="inlineStr">
@@ -53842,7 +53842,7 @@
       </c>
       <c r="AJ283" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK283" t="inlineStr">
@@ -54241,7 +54241,7 @@
       </c>
       <c r="AJ285" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK285" t="inlineStr">
@@ -54640,7 +54640,7 @@
       </c>
       <c r="AJ287" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK287" t="inlineStr">
@@ -55039,7 +55039,7 @@
       </c>
       <c r="AJ289" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK289" t="inlineStr">
@@ -55435,7 +55435,7 @@
       </c>
       <c r="AJ291" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK291" t="inlineStr">
@@ -56375,7 +56375,7 @@
       </c>
       <c r="AJ296" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK296" t="inlineStr">
@@ -56774,7 +56774,7 @@
       </c>
       <c r="AJ298" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK298" t="inlineStr">
@@ -57173,7 +57173,7 @@
       </c>
       <c r="AJ300" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK300" t="inlineStr">
@@ -57572,7 +57572,7 @@
       </c>
       <c r="AJ302" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK302" t="inlineStr">
@@ -57971,7 +57971,7 @@
       </c>
       <c r="AJ304" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK304" t="inlineStr">
@@ -58367,7 +58367,7 @@
       </c>
       <c r="AJ306" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK306" t="inlineStr">
@@ -59307,7 +59307,7 @@
       </c>
       <c r="AJ311" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK311" t="inlineStr">
@@ -59706,7 +59706,7 @@
       </c>
       <c r="AJ313" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK313" t="inlineStr">
@@ -60105,7 +60105,7 @@
       </c>
       <c r="AJ315" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK315" t="inlineStr">
@@ -60504,7 +60504,7 @@
       </c>
       <c r="AJ317" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK317" t="inlineStr">
@@ -60900,7 +60900,7 @@
       </c>
       <c r="AJ319" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK319" t="inlineStr">
@@ -61840,7 +61840,7 @@
       </c>
       <c r="AJ324" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK324" t="inlineStr">
@@ -62239,7 +62239,7 @@
       </c>
       <c r="AJ326" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK326" t="inlineStr">
@@ -62638,7 +62638,7 @@
       </c>
       <c r="AJ328" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK328" t="inlineStr">
@@ -63037,7 +63037,7 @@
       </c>
       <c r="AJ330" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK330" t="inlineStr">
@@ -63433,7 +63433,7 @@
       </c>
       <c r="AJ332" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK332" t="inlineStr">
@@ -64373,7 +64373,7 @@
       </c>
       <c r="AJ337" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK337" t="inlineStr">
@@ -64772,7 +64772,7 @@
       </c>
       <c r="AJ339" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK339" t="inlineStr">
@@ -65171,7 +65171,7 @@
       </c>
       <c r="AJ341" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK341" t="inlineStr">
@@ -65570,7 +65570,7 @@
       </c>
       <c r="AJ343" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK343" t="inlineStr">
@@ -65969,7 +65969,7 @@
       </c>
       <c r="AJ345" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK345" t="inlineStr">
@@ -66365,7 +66365,7 @@
       </c>
       <c r="AJ347" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK347" t="inlineStr">
@@ -67305,7 +67305,7 @@
       </c>
       <c r="AJ352" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK352" t="inlineStr">
@@ -67704,7 +67704,7 @@
       </c>
       <c r="AJ354" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK354" t="inlineStr">
@@ -68103,7 +68103,7 @@
       </c>
       <c r="AJ356" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK356" t="inlineStr">
@@ -68502,7 +68502,7 @@
       </c>
       <c r="AJ358" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK358" t="inlineStr">
@@ -68898,7 +68898,7 @@
       </c>
       <c r="AJ360" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK360" t="inlineStr">
@@ -69838,7 +69838,7 @@
       </c>
       <c r="AJ365" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK365" t="inlineStr">
@@ -70237,7 +70237,7 @@
       </c>
       <c r="AJ367" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK367" t="inlineStr">
@@ -70636,7 +70636,7 @@
       </c>
       <c r="AJ369" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK369" t="inlineStr">
@@ -71035,7 +71035,7 @@
       </c>
       <c r="AJ371" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK371" t="inlineStr">
@@ -71434,7 +71434,7 @@
       </c>
       <c r="AJ373" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK373" t="inlineStr">
@@ -71830,7 +71830,7 @@
       </c>
       <c r="AJ375" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK375" t="inlineStr">
@@ -72770,7 +72770,7 @@
       </c>
       <c r="AJ380" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK380" t="inlineStr">
@@ -73169,7 +73169,7 @@
       </c>
       <c r="AJ382" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK382" t="inlineStr">
@@ -73568,7 +73568,7 @@
       </c>
       <c r="AJ384" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK384" t="inlineStr">
@@ -73967,7 +73967,7 @@
       </c>
       <c r="AJ386" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK386" t="inlineStr">
@@ -74363,7 +74363,7 @@
       </c>
       <c r="AJ388" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK388" t="inlineStr">
@@ -75303,7 +75303,7 @@
       </c>
       <c r="AJ393" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK393" t="inlineStr">
@@ -75702,7 +75702,7 @@
       </c>
       <c r="AJ395" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK395" t="inlineStr">
@@ -76101,7 +76101,7 @@
       </c>
       <c r="AJ397" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK397" t="inlineStr">
@@ -76500,7 +76500,7 @@
       </c>
       <c r="AJ399" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK399" t="inlineStr">
@@ -76896,7 +76896,7 @@
       </c>
       <c r="AJ401" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK401" t="inlineStr">
@@ -77836,7 +77836,7 @@
       </c>
       <c r="AJ406" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK406" t="inlineStr">
@@ -78235,7 +78235,7 @@
       </c>
       <c r="AJ408" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK408" t="inlineStr">
@@ -78634,7 +78634,7 @@
       </c>
       <c r="AJ410" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK410" t="inlineStr">
@@ -79033,7 +79033,7 @@
       </c>
       <c r="AJ412" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK412" t="inlineStr">
@@ -79432,7 +79432,7 @@
       </c>
       <c r="AJ414" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK414" t="inlineStr">
@@ -79828,7 +79828,7 @@
       </c>
       <c r="AJ416" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK416" t="inlineStr">
@@ -80768,7 +80768,7 @@
       </c>
       <c r="AJ421" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK421" t="inlineStr">
@@ -81167,7 +81167,7 @@
       </c>
       <c r="AJ423" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK423" t="inlineStr">
@@ -81566,7 +81566,7 @@
       </c>
       <c r="AJ425" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK425" t="inlineStr">
@@ -81965,7 +81965,7 @@
       </c>
       <c r="AJ427" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK427" t="inlineStr">
